--- a/Techniques/Univariate Statistical Monitoring/outputs/G11/dsas_g11_bearings_vibration_temp_univariate/univariate/dsas_g11_univariate_output3.xlsx
+++ b/Techniques/Univariate Statistical Monitoring/outputs/G11/dsas_g11_bearings_vibration_temp_univariate/univariate/dsas_g11_univariate_output3.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="EWMA_Comparison" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Baseline_Stats" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EWMA_Comparison" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Baseline_Stats" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -21,13 +21,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -38,7 +41,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -46,12 +49,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -422,29 +434,29 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>AssetID</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>EWMA</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>46116.3550925926</v>
       </c>
       <c r="B2" t="inlineStr">
@@ -460,7 +472,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>46116.52167824074</v>
       </c>
       <c r="B3" t="inlineStr">
@@ -476,7 +488,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>46116.69474537037</v>
       </c>
       <c r="B4" t="inlineStr">
@@ -492,7 +504,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>46116.85944444445</v>
       </c>
       <c r="B5" t="inlineStr">
@@ -508,7 +520,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>46117.03664351852</v>
       </c>
       <c r="B6" t="inlineStr">
@@ -524,7 +536,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>46117.24065972222</v>
       </c>
       <c r="B7" t="inlineStr">
@@ -540,7 +552,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>46117.36049768519</v>
       </c>
       <c r="B8" t="inlineStr">
@@ -556,7 +568,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>46117.52633101852</v>
       </c>
       <c r="B9" t="inlineStr">
@@ -572,7 +584,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>46117.69008101852</v>
       </c>
       <c r="B10" t="inlineStr">
@@ -588,7 +600,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>46117.87108796297</v>
       </c>
       <c r="B11" t="inlineStr">
@@ -604,7 +616,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>46118.0265625</v>
       </c>
       <c r="B12" t="inlineStr">
@@ -620,7 +632,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>46118.19368055555</v>
       </c>
       <c r="B13" t="inlineStr">
@@ -636,7 +648,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>46118.36050925926</v>
       </c>
       <c r="B14" t="inlineStr">
@@ -652,7 +664,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>46118.52253472222</v>
       </c>
       <c r="B15" t="inlineStr">
@@ -668,7 +680,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>46118.68907407407</v>
       </c>
       <c r="B16" t="inlineStr">
@@ -684,7 +696,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>46118.8552662037</v>
       </c>
       <c r="B17" t="inlineStr">
@@ -700,7 +712,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>46119.02732638889</v>
       </c>
       <c r="B18" t="inlineStr">
@@ -716,7 +728,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>46120.18833333333</v>
       </c>
       <c r="B19" t="inlineStr">
@@ -732,7 +744,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>46120.52369212963</v>
       </c>
       <c r="B20" t="inlineStr">
@@ -748,7 +760,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>46120.69190972222</v>
       </c>
       <c r="B21" t="inlineStr">
@@ -764,7 +776,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>46120.85443287037</v>
       </c>
       <c r="B22" t="inlineStr">
@@ -780,7 +792,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>46124.39263888889</v>
       </c>
       <c r="B23" t="inlineStr">
@@ -796,7 +808,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>46124.52407407408</v>
       </c>
       <c r="B24" t="inlineStr">
@@ -812,7 +824,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>46124.69166666667</v>
       </c>
       <c r="B25" t="inlineStr">
@@ -828,7 +840,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>46124.85614583334</v>
       </c>
       <c r="B26" t="inlineStr">
@@ -844,7 +856,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>46125.07673611111</v>
       </c>
       <c r="B27" t="inlineStr">
@@ -860,7 +872,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>46125.18878472222</v>
       </c>
       <c r="B28" t="inlineStr">
@@ -876,7 +888,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>46125.37304398148</v>
       </c>
       <c r="B29" t="inlineStr">
@@ -892,7 +904,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>46125.52486111111</v>
       </c>
       <c r="B30" t="inlineStr">
@@ -908,7 +920,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>46125.69287037037</v>
       </c>
       <c r="B31" t="inlineStr">
@@ -924,7 +936,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>46125.85716435185</v>
       </c>
       <c r="B32" t="inlineStr">
@@ -940,7 +952,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>46126.03134259259</v>
       </c>
       <c r="B33" t="inlineStr">
@@ -956,7 +968,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>46126.21274305556</v>
       </c>
       <c r="B34" t="inlineStr">
@@ -972,7 +984,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>46126.35861111111</v>
       </c>
       <c r="B35" t="inlineStr">
@@ -988,7 +1000,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>46126.53461805556</v>
       </c>
       <c r="B36" t="inlineStr">
@@ -1004,7 +1016,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>46126.70118055555</v>
       </c>
       <c r="B37" t="inlineStr">
@@ -1020,7 +1032,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>46126.87692129629</v>
       </c>
       <c r="B38" t="inlineStr">
@@ -1036,7 +1048,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>46127.02172453704</v>
       </c>
       <c r="B39" t="inlineStr">
@@ -1052,7 +1064,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>46127.20758101852</v>
       </c>
       <c r="B40" t="inlineStr">
@@ -1068,7 +1080,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>46127.35572916667</v>
       </c>
       <c r="B41" t="inlineStr">
@@ -1084,7 +1096,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>46127.53050925926</v>
       </c>
       <c r="B42" t="inlineStr">
@@ -1100,7 +1112,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>46127.69168981481</v>
       </c>
       <c r="B43" t="inlineStr">
@@ -1116,7 +1128,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>46127.85546296297</v>
       </c>
       <c r="B44" t="inlineStr">
@@ -1132,7 +1144,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>46128.04122685185</v>
       </c>
       <c r="B45" t="inlineStr">
@@ -1148,7 +1160,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>46128.19846064815</v>
       </c>
       <c r="B46" t="inlineStr">
@@ -1164,7 +1176,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>46128.3578125</v>
       </c>
       <c r="B47" t="inlineStr">
@@ -1180,7 +1192,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>46128.52149305555</v>
       </c>
       <c r="B48" t="inlineStr">
@@ -1196,7 +1208,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>46128.69186342593</v>
       </c>
       <c r="B49" t="inlineStr">
@@ -1212,7 +1224,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>46128.85454861111</v>
       </c>
       <c r="B50" t="inlineStr">
@@ -1228,7 +1240,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>46129.08709490741</v>
       </c>
       <c r="B51" t="inlineStr">
@@ -1244,7 +1256,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>46129.20550925926</v>
       </c>
       <c r="B52" t="inlineStr">
@@ -1260,7 +1272,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>46129.36481481481</v>
       </c>
       <c r="B53" t="inlineStr">
@@ -1276,7 +1288,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>46129.52703703703</v>
       </c>
       <c r="B54" t="inlineStr">
@@ -1292,7 +1304,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>46129.69325231481</v>
       </c>
       <c r="B55" t="inlineStr">
@@ -1308,7 +1320,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>46129.85914351852</v>
       </c>
       <c r="B56" t="inlineStr">
@@ -1324,7 +1336,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>46130.09744212963</v>
       </c>
       <c r="B57" t="inlineStr">
@@ -1340,7 +1352,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>46130.19385416667</v>
       </c>
       <c r="B58" t="inlineStr">
@@ -1356,7 +1368,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>46130.35618055556</v>
       </c>
       <c r="B59" t="inlineStr">
@@ -1372,7 +1384,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>46130.52403935185</v>
       </c>
       <c r="B60" t="inlineStr">
@@ -1388,7 +1400,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>46130.68988425926</v>
       </c>
       <c r="B61" t="inlineStr">
@@ -1404,7 +1416,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>46131.02777777778</v>
       </c>
       <c r="B62" t="inlineStr">
@@ -1420,7 +1432,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>46131.19017361111</v>
       </c>
       <c r="B63" t="inlineStr">
@@ -1436,7 +1448,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>46131.35472222222</v>
       </c>
       <c r="B64" t="inlineStr">
@@ -1452,7 +1464,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>46131.52929398148</v>
       </c>
       <c r="B65" t="inlineStr">
@@ -1468,7 +1480,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>46131.68760416667</v>
       </c>
       <c r="B66" t="inlineStr">
@@ -1484,7 +1496,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>46131.8633912037</v>
       </c>
       <c r="B67" t="inlineStr">
@@ -1500,7 +1512,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>46132.02103009259</v>
       </c>
       <c r="B68" t="inlineStr">
@@ -1516,7 +1528,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>46132.19717592592</v>
       </c>
       <c r="B69" t="inlineStr">
@@ -1532,7 +1544,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>46132.3584375</v>
       </c>
       <c r="B70" t="inlineStr">
@@ -1548,7 +1560,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>46132.52159722222</v>
       </c>
       <c r="B71" t="inlineStr">
@@ -1564,7 +1576,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>46132.69394675926</v>
       </c>
       <c r="B72" t="inlineStr">
@@ -1580,7 +1592,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>46132.86247685185</v>
       </c>
       <c r="B73" t="inlineStr">
@@ -1596,7 +1608,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>46133.07111111111</v>
       </c>
       <c r="B74" t="inlineStr">
@@ -1612,7 +1624,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>46133.19524305555</v>
       </c>
       <c r="B75" t="inlineStr">
@@ -1628,7 +1640,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>46133.36118055556</v>
       </c>
       <c r="B76" t="inlineStr">
@@ -1644,7 +1656,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>46133.52528935186</v>
       </c>
       <c r="B77" t="inlineStr">
@@ -1660,7 +1672,7 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>46133.69530092592</v>
       </c>
       <c r="B78" t="inlineStr">
@@ -1676,7 +1688,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>46133.85505787037</v>
       </c>
       <c r="B79" t="inlineStr">
@@ -1692,7 +1704,7 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="2" t="n">
         <v>46134.09811342593</v>
       </c>
       <c r="B80" t="inlineStr">
@@ -1708,7 +1720,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>46134.21712962963</v>
       </c>
       <c r="B81" t="inlineStr">
@@ -1724,7 +1736,7 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>46134.35688657407</v>
       </c>
       <c r="B82" t="inlineStr">
@@ -1740,7 +1752,7 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>46134.52453703704</v>
       </c>
       <c r="B83" t="inlineStr">
@@ -1756,7 +1768,7 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="2" t="n">
         <v>46134.72311342593</v>
       </c>
       <c r="B84" t="inlineStr">
@@ -1772,7 +1784,7 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="2" t="n">
         <v>46134.85905092592</v>
       </c>
       <c r="B85" t="inlineStr">
@@ -1788,7 +1800,7 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" s="2" t="n">
         <v>46135.02693287037</v>
       </c>
       <c r="B86" t="inlineStr">
@@ -1804,7 +1816,7 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" s="2" t="n">
         <v>46135.19215277778</v>
       </c>
       <c r="B87" t="inlineStr">
@@ -1820,7 +1832,7 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" s="2" t="n">
         <v>46135.3603125</v>
       </c>
       <c r="B88" t="inlineStr">
@@ -1836,7 +1848,7 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" s="2" t="n">
         <v>46135.53359953704</v>
       </c>
       <c r="B89" t="inlineStr">
@@ -1852,7 +1864,7 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" s="2" t="n">
         <v>46135.68820601852</v>
       </c>
       <c r="B90" t="inlineStr">
@@ -1868,7 +1880,7 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" s="2" t="n">
         <v>46135.86390046297</v>
       </c>
       <c r="B91" t="inlineStr">
@@ -1884,7 +1896,7 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" s="2" t="n">
         <v>46136.02126157407</v>
       </c>
       <c r="B92" t="inlineStr">
@@ -1900,7 +1912,7 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" s="2" t="n">
         <v>46136.18943287037</v>
       </c>
       <c r="B93" t="inlineStr">
@@ -1916,7 +1928,7 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" s="2" t="n">
         <v>46136.35768518518</v>
       </c>
       <c r="B94" t="inlineStr">
@@ -1932,7 +1944,7 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" s="2" t="n">
         <v>46136.52224537037</v>
       </c>
       <c r="B95" t="inlineStr">
@@ -1948,7 +1960,7 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" s="2" t="n">
         <v>46136.6883912037</v>
       </c>
       <c r="B96" t="inlineStr">
@@ -1964,7 +1976,7 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" s="2" t="n">
         <v>46136.85456018519</v>
       </c>
       <c r="B97" t="inlineStr">
@@ -1980,7 +1992,7 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" s="2" t="n">
         <v>46137.0588425926</v>
       </c>
       <c r="B98" t="inlineStr">
@@ -1996,7 +2008,7 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" s="2" t="n">
         <v>46137.18950231482</v>
       </c>
       <c r="B99" t="inlineStr">
@@ -2012,7 +2024,7 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" s="2" t="n">
         <v>46137.36697916667</v>
       </c>
       <c r="B100" t="inlineStr">
@@ -2028,7 +2040,7 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" s="2" t="n">
         <v>46137.52636574074</v>
       </c>
       <c r="B101" t="inlineStr">
@@ -2044,7 +2056,7 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
+      <c r="A102" s="2" t="n">
         <v>46137.68905092592</v>
       </c>
       <c r="B102" t="inlineStr">
@@ -2060,7 +2072,7 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
+      <c r="A103" s="2" t="n">
         <v>46137.8555787037</v>
       </c>
       <c r="B103" t="inlineStr">
@@ -2076,7 +2088,7 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
+      <c r="A104" s="2" t="n">
         <v>46138.08900462963</v>
       </c>
       <c r="B104" t="inlineStr">
@@ -2092,7 +2104,7 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
+      <c r="A105" s="2" t="n">
         <v>46138.22342592593</v>
       </c>
       <c r="B105" t="inlineStr">
@@ -2108,7 +2120,7 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
+      <c r="A106" s="2" t="n">
         <v>46138.35784722222</v>
       </c>
       <c r="B106" t="inlineStr">
@@ -2124,7 +2136,7 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
+      <c r="A107" s="2" t="n">
         <v>46138.54626157408</v>
       </c>
       <c r="B107" t="inlineStr">
@@ -2140,7 +2152,7 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
+      <c r="A108" s="2" t="n">
         <v>46138.69407407408</v>
       </c>
       <c r="B108" t="inlineStr">
@@ -2156,7 +2168,7 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
+      <c r="A109" s="2" t="n">
         <v>46138.85946759259</v>
       </c>
       <c r="B109" t="inlineStr">
@@ -2172,7 +2184,7 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
+      <c r="A110" s="2" t="n">
         <v>46139.04685185185</v>
       </c>
       <c r="B110" t="inlineStr">
@@ -2188,7 +2200,7 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
+      <c r="A111" s="2" t="n">
         <v>46139.20314814815</v>
       </c>
       <c r="B111" t="inlineStr">
@@ -2204,7 +2216,7 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
+      <c r="A112" s="2" t="n">
         <v>46139.35634259259</v>
       </c>
       <c r="B112" t="inlineStr">
@@ -2220,7 +2232,7 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
+      <c r="A113" s="2" t="n">
         <v>46139.52431712963</v>
       </c>
       <c r="B113" t="inlineStr">
@@ -2236,7 +2248,7 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
+      <c r="A114" s="2" t="n">
         <v>46139.69873842593</v>
       </c>
       <c r="B114" t="inlineStr">
@@ -2252,7 +2264,7 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n">
+      <c r="A115" s="2" t="n">
         <v>46139.86931712963</v>
       </c>
       <c r="B115" t="inlineStr">
@@ -2268,7 +2280,7 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="n">
+      <c r="A116" s="2" t="n">
         <v>46140.02158564814</v>
       </c>
       <c r="B116" t="inlineStr">
@@ -2284,7 +2296,7 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
+      <c r="A117" s="2" t="n">
         <v>46140.19370370371</v>
       </c>
       <c r="B117" t="inlineStr">
@@ -2300,7 +2312,7 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
+      <c r="A118" s="2" t="n">
         <v>46140.35989583333</v>
       </c>
       <c r="B118" t="inlineStr">
@@ -2316,7 +2328,7 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
+      <c r="A119" s="2" t="n">
         <v>46140.52547453704</v>
       </c>
       <c r="B119" t="inlineStr">
@@ -2332,7 +2344,7 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
+      <c r="A120" s="2" t="n">
         <v>46140.69204861111</v>
       </c>
       <c r="B120" t="inlineStr">
@@ -2348,7 +2360,7 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="n">
+      <c r="A121" s="2" t="n">
         <v>46140.85797453704</v>
       </c>
       <c r="B121" t="inlineStr">
@@ -2364,7 +2376,7 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="n">
+      <c r="A122" s="2" t="n">
         <v>46141.08907407407</v>
       </c>
       <c r="B122" t="inlineStr">
@@ -2380,7 +2392,7 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="n">
+      <c r="A123" s="2" t="n">
         <v>46141.19405092593</v>
       </c>
       <c r="B123" t="inlineStr">
@@ -2396,7 +2408,7 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
+      <c r="A124" s="2" t="n">
         <v>46141.37282407407</v>
       </c>
       <c r="B124" t="inlineStr">
@@ -2412,7 +2424,7 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="n">
+      <c r="A125" s="2" t="n">
         <v>46141.52434027778</v>
       </c>
       <c r="B125" t="inlineStr">
@@ -2428,7 +2440,7 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="n">
+      <c r="A126" s="2" t="n">
         <v>46141.69369212963</v>
       </c>
       <c r="B126" t="inlineStr">
@@ -2444,7 +2456,7 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="n">
+      <c r="A127" s="2" t="n">
         <v>46141.85452546296</v>
       </c>
       <c r="B127" t="inlineStr">
@@ -2460,7 +2472,7 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="n">
+      <c r="A128" s="2" t="n">
         <v>46142.09556712963</v>
       </c>
       <c r="B128" t="inlineStr">
@@ -2476,7 +2488,7 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="1" t="n">
+      <c r="A129" s="2" t="n">
         <v>46142.22015046296</v>
       </c>
       <c r="B129" t="inlineStr">
@@ -2492,7 +2504,7 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="n">
+      <c r="A130" s="2" t="n">
         <v>46142.35427083333</v>
       </c>
       <c r="B130" t="inlineStr">
@@ -2508,7 +2520,7 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="n">
+      <c r="A131" s="2" t="n">
         <v>46142.52810185185</v>
       </c>
       <c r="B131" t="inlineStr">
@@ -2524,7 +2536,7 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="1" t="n">
+      <c r="A132" s="2" t="n">
         <v>46142.70089120371</v>
       </c>
       <c r="B132" t="inlineStr">
@@ -2540,7 +2552,7 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="1" t="n">
+      <c r="A133" s="2" t="n">
         <v>46142.85965277778</v>
       </c>
       <c r="B133" t="inlineStr">
@@ -2556,7 +2568,7 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="1" t="n">
+      <c r="A134" s="2" t="n">
         <v>46143.02594907407</v>
       </c>
       <c r="B134" t="inlineStr">
@@ -2572,7 +2584,7 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="1" t="n">
+      <c r="A135" s="2" t="n">
         <v>46143.20488425926</v>
       </c>
       <c r="B135" t="inlineStr">
@@ -2588,7 +2600,7 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="1" t="n">
+      <c r="A136" s="2" t="n">
         <v>46143.35506944444</v>
       </c>
       <c r="B136" t="inlineStr">
@@ -2604,7 +2616,7 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="1" t="n">
+      <c r="A137" s="2" t="n">
         <v>46143.52101851852</v>
       </c>
       <c r="B137" t="inlineStr">
@@ -2620,7 +2632,7 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="1" t="n">
+      <c r="A138" s="2" t="n">
         <v>46143.69318287037</v>
       </c>
       <c r="B138" t="inlineStr">
@@ -2636,7 +2648,7 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="1" t="n">
+      <c r="A139" s="2" t="n">
         <v>46143.86835648148</v>
       </c>
       <c r="B139" t="inlineStr">
@@ -2652,7 +2664,7 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="1" t="n">
+      <c r="A140" s="2" t="n">
         <v>46144.02177083334</v>
       </c>
       <c r="B140" t="inlineStr">
@@ -2668,7 +2680,7 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="1" t="n">
+      <c r="A141" s="2" t="n">
         <v>46144.18803240741</v>
       </c>
       <c r="B141" t="inlineStr">
@@ -2684,7 +2696,7 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="1" t="n">
+      <c r="A142" s="2" t="n">
         <v>46144.35827546296</v>
       </c>
       <c r="B142" t="inlineStr">
@@ -2700,7 +2712,7 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="1" t="n">
+      <c r="A143" s="2" t="n">
         <v>46144.52101851852</v>
       </c>
       <c r="B143" t="inlineStr">
@@ -2716,7 +2728,7 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="1" t="n">
+      <c r="A144" s="2" t="n">
         <v>46144.69450231481</v>
       </c>
       <c r="B144" t="inlineStr">
@@ -2732,7 +2744,7 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="1" t="n">
+      <c r="A145" s="2" t="n">
         <v>46144.85748842593</v>
       </c>
       <c r="B145" t="inlineStr">
@@ -2748,7 +2760,7 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="1" t="n">
+      <c r="A146" s="2" t="n">
         <v>46145.06841435185</v>
       </c>
       <c r="B146" t="inlineStr">
@@ -2764,7 +2776,7 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="1" t="n">
+      <c r="A147" s="2" t="n">
         <v>46145.20671296296</v>
       </c>
       <c r="B147" t="inlineStr">
@@ -2780,7 +2792,7 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="1" t="n">
+      <c r="A148" s="2" t="n">
         <v>46145.35491898148</v>
       </c>
       <c r="B148" t="inlineStr">
@@ -2796,7 +2808,7 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="1" t="n">
+      <c r="A149" s="2" t="n">
         <v>46145.52814814815</v>
       </c>
       <c r="B149" t="inlineStr">
@@ -2812,7 +2824,7 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="1" t="n">
+      <c r="A150" s="2" t="n">
         <v>46145.69175925926</v>
       </c>
       <c r="B150" t="inlineStr">
@@ -2828,7 +2840,7 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="1" t="n">
+      <c r="A151" s="2" t="n">
         <v>46145.85527777778</v>
       </c>
       <c r="B151" t="inlineStr">
@@ -2844,7 +2856,7 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="1" t="n">
+      <c r="A152" s="2" t="n">
         <v>46146.09436342592</v>
       </c>
       <c r="B152" t="inlineStr">
@@ -2860,7 +2872,7 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="1" t="n">
+      <c r="A153" s="2" t="n">
         <v>46146.21984953704</v>
       </c>
       <c r="B153" t="inlineStr">
@@ -2876,7 +2888,7 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="1" t="n">
+      <c r="A154" s="2" t="n">
         <v>46116.3550925926</v>
       </c>
       <c r="B154" t="inlineStr">
@@ -2892,7 +2904,7 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="1" t="n">
+      <c r="A155" s="2" t="n">
         <v>46116.52167824074</v>
       </c>
       <c r="B155" t="inlineStr">
@@ -2908,7 +2920,7 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="1" t="n">
+      <c r="A156" s="2" t="n">
         <v>46116.69474537037</v>
       </c>
       <c r="B156" t="inlineStr">
@@ -2924,7 +2936,7 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="1" t="n">
+      <c r="A157" s="2" t="n">
         <v>46116.85944444445</v>
       </c>
       <c r="B157" t="inlineStr">
@@ -2940,7 +2952,7 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="1" t="n">
+      <c r="A158" s="2" t="n">
         <v>46117.03664351852</v>
       </c>
       <c r="B158" t="inlineStr">
@@ -2956,7 +2968,7 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="1" t="n">
+      <c r="A159" s="2" t="n">
         <v>46117.24065972222</v>
       </c>
       <c r="B159" t="inlineStr">
@@ -2972,7 +2984,7 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="1" t="n">
+      <c r="A160" s="2" t="n">
         <v>46117.36049768519</v>
       </c>
       <c r="B160" t="inlineStr">
@@ -2988,7 +3000,7 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="1" t="n">
+      <c r="A161" s="2" t="n">
         <v>46117.52633101852</v>
       </c>
       <c r="B161" t="inlineStr">
@@ -3004,7 +3016,7 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="1" t="n">
+      <c r="A162" s="2" t="n">
         <v>46117.69008101852</v>
       </c>
       <c r="B162" t="inlineStr">
@@ -3020,7 +3032,7 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="1" t="n">
+      <c r="A163" s="2" t="n">
         <v>46117.87108796297</v>
       </c>
       <c r="B163" t="inlineStr">
@@ -3036,7 +3048,7 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="1" t="n">
+      <c r="A164" s="2" t="n">
         <v>46118.0265625</v>
       </c>
       <c r="B164" t="inlineStr">
@@ -3052,7 +3064,7 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="1" t="n">
+      <c r="A165" s="2" t="n">
         <v>46118.19368055555</v>
       </c>
       <c r="B165" t="inlineStr">
@@ -3068,7 +3080,7 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="1" t="n">
+      <c r="A166" s="2" t="n">
         <v>46118.36050925926</v>
       </c>
       <c r="B166" t="inlineStr">
@@ -3084,7 +3096,7 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="1" t="n">
+      <c r="A167" s="2" t="n">
         <v>46118.52253472222</v>
       </c>
       <c r="B167" t="inlineStr">
@@ -3100,7 +3112,7 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="1" t="n">
+      <c r="A168" s="2" t="n">
         <v>46118.68907407407</v>
       </c>
       <c r="B168" t="inlineStr">
@@ -3116,7 +3128,7 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="1" t="n">
+      <c r="A169" s="2" t="n">
         <v>46118.8552662037</v>
       </c>
       <c r="B169" t="inlineStr">
@@ -3132,7 +3144,7 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="1" t="n">
+      <c r="A170" s="2" t="n">
         <v>46119.02732638889</v>
       </c>
       <c r="B170" t="inlineStr">
@@ -3148,7 +3160,7 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="1" t="n">
+      <c r="A171" s="2" t="n">
         <v>46120.18833333333</v>
       </c>
       <c r="B171" t="inlineStr">
@@ -3164,7 +3176,7 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="1" t="n">
+      <c r="A172" s="2" t="n">
         <v>46120.52369212963</v>
       </c>
       <c r="B172" t="inlineStr">
@@ -3180,7 +3192,7 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="1" t="n">
+      <c r="A173" s="2" t="n">
         <v>46120.69190972222</v>
       </c>
       <c r="B173" t="inlineStr">
@@ -3196,7 +3208,7 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="1" t="n">
+      <c r="A174" s="2" t="n">
         <v>46120.85443287037</v>
       </c>
       <c r="B174" t="inlineStr">
@@ -3212,7 +3224,7 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="1" t="n">
+      <c r="A175" s="2" t="n">
         <v>46124.39263888889</v>
       </c>
       <c r="B175" t="inlineStr">
@@ -3228,7 +3240,7 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="1" t="n">
+      <c r="A176" s="2" t="n">
         <v>46124.52407407408</v>
       </c>
       <c r="B176" t="inlineStr">
@@ -3244,7 +3256,7 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="1" t="n">
+      <c r="A177" s="2" t="n">
         <v>46124.69166666667</v>
       </c>
       <c r="B177" t="inlineStr">
@@ -3260,7 +3272,7 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="1" t="n">
+      <c r="A178" s="2" t="n">
         <v>46124.85614583334</v>
       </c>
       <c r="B178" t="inlineStr">
@@ -3276,7 +3288,7 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="1" t="n">
+      <c r="A179" s="2" t="n">
         <v>46125.07673611111</v>
       </c>
       <c r="B179" t="inlineStr">
@@ -3292,7 +3304,7 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="1" t="n">
+      <c r="A180" s="2" t="n">
         <v>46125.18878472222</v>
       </c>
       <c r="B180" t="inlineStr">
@@ -3308,7 +3320,7 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="1" t="n">
+      <c r="A181" s="2" t="n">
         <v>46125.37304398148</v>
       </c>
       <c r="B181" t="inlineStr">
@@ -3324,7 +3336,7 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="1" t="n">
+      <c r="A182" s="2" t="n">
         <v>46125.52486111111</v>
       </c>
       <c r="B182" t="inlineStr">
@@ -3340,7 +3352,7 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="1" t="n">
+      <c r="A183" s="2" t="n">
         <v>46125.69287037037</v>
       </c>
       <c r="B183" t="inlineStr">
@@ -3356,7 +3368,7 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="1" t="n">
+      <c r="A184" s="2" t="n">
         <v>46125.85716435185</v>
       </c>
       <c r="B184" t="inlineStr">
@@ -3372,7 +3384,7 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="1" t="n">
+      <c r="A185" s="2" t="n">
         <v>46126.03134259259</v>
       </c>
       <c r="B185" t="inlineStr">
@@ -3388,7 +3400,7 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="1" t="n">
+      <c r="A186" s="2" t="n">
         <v>46126.21274305556</v>
       </c>
       <c r="B186" t="inlineStr">
@@ -3404,7 +3416,7 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="1" t="n">
+      <c r="A187" s="2" t="n">
         <v>46126.35861111111</v>
       </c>
       <c r="B187" t="inlineStr">
@@ -3420,7 +3432,7 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="1" t="n">
+      <c r="A188" s="2" t="n">
         <v>46126.53461805556</v>
       </c>
       <c r="B188" t="inlineStr">
@@ -3436,7 +3448,7 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="1" t="n">
+      <c r="A189" s="2" t="n">
         <v>46126.70118055555</v>
       </c>
       <c r="B189" t="inlineStr">
@@ -3452,7 +3464,7 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="1" t="n">
+      <c r="A190" s="2" t="n">
         <v>46126.87692129629</v>
       </c>
       <c r="B190" t="inlineStr">
@@ -3468,7 +3480,7 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="1" t="n">
+      <c r="A191" s="2" t="n">
         <v>46127.02172453704</v>
       </c>
       <c r="B191" t="inlineStr">
@@ -3484,7 +3496,7 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="1" t="n">
+      <c r="A192" s="2" t="n">
         <v>46127.20758101852</v>
       </c>
       <c r="B192" t="inlineStr">
@@ -3500,7 +3512,7 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="1" t="n">
+      <c r="A193" s="2" t="n">
         <v>46127.35572916667</v>
       </c>
       <c r="B193" t="inlineStr">
@@ -3516,7 +3528,7 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="1" t="n">
+      <c r="A194" s="2" t="n">
         <v>46127.53050925926</v>
       </c>
       <c r="B194" t="inlineStr">
@@ -3532,7 +3544,7 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="1" t="n">
+      <c r="A195" s="2" t="n">
         <v>46127.69168981481</v>
       </c>
       <c r="B195" t="inlineStr">
@@ -3548,7 +3560,7 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="1" t="n">
+      <c r="A196" s="2" t="n">
         <v>46127.85546296297</v>
       </c>
       <c r="B196" t="inlineStr">
@@ -3564,7 +3576,7 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="1" t="n">
+      <c r="A197" s="2" t="n">
         <v>46128.04122685185</v>
       </c>
       <c r="B197" t="inlineStr">
@@ -3580,7 +3592,7 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="1" t="n">
+      <c r="A198" s="2" t="n">
         <v>46128.19846064815</v>
       </c>
       <c r="B198" t="inlineStr">
@@ -3596,7 +3608,7 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="1" t="n">
+      <c r="A199" s="2" t="n">
         <v>46128.3578125</v>
       </c>
       <c r="B199" t="inlineStr">
@@ -3612,7 +3624,7 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="1" t="n">
+      <c r="A200" s="2" t="n">
         <v>46128.52149305555</v>
       </c>
       <c r="B200" t="inlineStr">
@@ -3628,7 +3640,7 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="1" t="n">
+      <c r="A201" s="2" t="n">
         <v>46128.69186342593</v>
       </c>
       <c r="B201" t="inlineStr">
@@ -3644,7 +3656,7 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="1" t="n">
+      <c r="A202" s="2" t="n">
         <v>46128.85454861111</v>
       </c>
       <c r="B202" t="inlineStr">
@@ -3660,7 +3672,7 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="1" t="n">
+      <c r="A203" s="2" t="n">
         <v>46129.08709490741</v>
       </c>
       <c r="B203" t="inlineStr">
@@ -3676,7 +3688,7 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="1" t="n">
+      <c r="A204" s="2" t="n">
         <v>46129.20550925926</v>
       </c>
       <c r="B204" t="inlineStr">
@@ -3692,7 +3704,7 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="1" t="n">
+      <c r="A205" s="2" t="n">
         <v>46129.36481481481</v>
       </c>
       <c r="B205" t="inlineStr">
@@ -3708,7 +3720,7 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="1" t="n">
+      <c r="A206" s="2" t="n">
         <v>46129.52703703703</v>
       </c>
       <c r="B206" t="inlineStr">
@@ -3724,7 +3736,7 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="1" t="n">
+      <c r="A207" s="2" t="n">
         <v>46129.69325231481</v>
       </c>
       <c r="B207" t="inlineStr">
@@ -3740,7 +3752,7 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="1" t="n">
+      <c r="A208" s="2" t="n">
         <v>46129.85914351852</v>
       </c>
       <c r="B208" t="inlineStr">
@@ -3756,7 +3768,7 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="1" t="n">
+      <c r="A209" s="2" t="n">
         <v>46130.09744212963</v>
       </c>
       <c r="B209" t="inlineStr">
@@ -3772,7 +3784,7 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="1" t="n">
+      <c r="A210" s="2" t="n">
         <v>46130.19385416667</v>
       </c>
       <c r="B210" t="inlineStr">
@@ -3788,7 +3800,7 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="1" t="n">
+      <c r="A211" s="2" t="n">
         <v>46130.35618055556</v>
       </c>
       <c r="B211" t="inlineStr">
@@ -3804,7 +3816,7 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="1" t="n">
+      <c r="A212" s="2" t="n">
         <v>46130.52403935185</v>
       </c>
       <c r="B212" t="inlineStr">
@@ -3820,7 +3832,7 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="1" t="n">
+      <c r="A213" s="2" t="n">
         <v>46130.68988425926</v>
       </c>
       <c r="B213" t="inlineStr">
@@ -3836,7 +3848,7 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="1" t="n">
+      <c r="A214" s="2" t="n">
         <v>46131.02777777778</v>
       </c>
       <c r="B214" t="inlineStr">
@@ -3852,7 +3864,7 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="1" t="n">
+      <c r="A215" s="2" t="n">
         <v>46131.19017361111</v>
       </c>
       <c r="B215" t="inlineStr">
@@ -3868,7 +3880,7 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="1" t="n">
+      <c r="A216" s="2" t="n">
         <v>46131.35472222222</v>
       </c>
       <c r="B216" t="inlineStr">
@@ -3884,7 +3896,7 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="1" t="n">
+      <c r="A217" s="2" t="n">
         <v>46131.52929398148</v>
       </c>
       <c r="B217" t="inlineStr">
@@ -3900,7 +3912,7 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="1" t="n">
+      <c r="A218" s="2" t="n">
         <v>46131.68760416667</v>
       </c>
       <c r="B218" t="inlineStr">
@@ -3916,7 +3928,7 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="1" t="n">
+      <c r="A219" s="2" t="n">
         <v>46131.8633912037</v>
       </c>
       <c r="B219" t="inlineStr">
@@ -3932,7 +3944,7 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="1" t="n">
+      <c r="A220" s="2" t="n">
         <v>46132.02103009259</v>
       </c>
       <c r="B220" t="inlineStr">
@@ -3948,7 +3960,7 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="1" t="n">
+      <c r="A221" s="2" t="n">
         <v>46132.19717592592</v>
       </c>
       <c r="B221" t="inlineStr">
@@ -3964,7 +3976,7 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="1" t="n">
+      <c r="A222" s="2" t="n">
         <v>46132.3584375</v>
       </c>
       <c r="B222" t="inlineStr">
@@ -3980,7 +3992,7 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="1" t="n">
+      <c r="A223" s="2" t="n">
         <v>46132.52159722222</v>
       </c>
       <c r="B223" t="inlineStr">
@@ -3996,7 +4008,7 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="1" t="n">
+      <c r="A224" s="2" t="n">
         <v>46132.69394675926</v>
       </c>
       <c r="B224" t="inlineStr">
@@ -4012,7 +4024,7 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="1" t="n">
+      <c r="A225" s="2" t="n">
         <v>46132.86247685185</v>
       </c>
       <c r="B225" t="inlineStr">
@@ -4028,7 +4040,7 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="1" t="n">
+      <c r="A226" s="2" t="n">
         <v>46133.07111111111</v>
       </c>
       <c r="B226" t="inlineStr">
@@ -4044,7 +4056,7 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="1" t="n">
+      <c r="A227" s="2" t="n">
         <v>46133.19524305555</v>
       </c>
       <c r="B227" t="inlineStr">
@@ -4060,7 +4072,7 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="1" t="n">
+      <c r="A228" s="2" t="n">
         <v>46133.36118055556</v>
       </c>
       <c r="B228" t="inlineStr">
@@ -4076,7 +4088,7 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="1" t="n">
+      <c r="A229" s="2" t="n">
         <v>46133.52528935186</v>
       </c>
       <c r="B229" t="inlineStr">
@@ -4092,7 +4104,7 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="1" t="n">
+      <c r="A230" s="2" t="n">
         <v>46133.69530092592</v>
       </c>
       <c r="B230" t="inlineStr">
@@ -4108,7 +4120,7 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="1" t="n">
+      <c r="A231" s="2" t="n">
         <v>46133.85505787037</v>
       </c>
       <c r="B231" t="inlineStr">
@@ -4124,7 +4136,7 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="1" t="n">
+      <c r="A232" s="2" t="n">
         <v>46134.09811342593</v>
       </c>
       <c r="B232" t="inlineStr">
@@ -4140,7 +4152,7 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="1" t="n">
+      <c r="A233" s="2" t="n">
         <v>46134.21712962963</v>
       </c>
       <c r="B233" t="inlineStr">
@@ -4156,7 +4168,7 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="1" t="n">
+      <c r="A234" s="2" t="n">
         <v>46134.35688657407</v>
       </c>
       <c r="B234" t="inlineStr">
@@ -4172,7 +4184,7 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="1" t="n">
+      <c r="A235" s="2" t="n">
         <v>46134.52453703704</v>
       </c>
       <c r="B235" t="inlineStr">
@@ -4188,7 +4200,7 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="1" t="n">
+      <c r="A236" s="2" t="n">
         <v>46134.72311342593</v>
       </c>
       <c r="B236" t="inlineStr">
@@ -4204,7 +4216,7 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="1" t="n">
+      <c r="A237" s="2" t="n">
         <v>46134.85905092592</v>
       </c>
       <c r="B237" t="inlineStr">
@@ -4220,7 +4232,7 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="1" t="n">
+      <c r="A238" s="2" t="n">
         <v>46135.02693287037</v>
       </c>
       <c r="B238" t="inlineStr">
@@ -4236,7 +4248,7 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="1" t="n">
+      <c r="A239" s="2" t="n">
         <v>46135.19215277778</v>
       </c>
       <c r="B239" t="inlineStr">
@@ -4252,7 +4264,7 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="1" t="n">
+      <c r="A240" s="2" t="n">
         <v>46135.3603125</v>
       </c>
       <c r="B240" t="inlineStr">
@@ -4268,7 +4280,7 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="1" t="n">
+      <c r="A241" s="2" t="n">
         <v>46135.53359953704</v>
       </c>
       <c r="B241" t="inlineStr">
@@ -4284,7 +4296,7 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="1" t="n">
+      <c r="A242" s="2" t="n">
         <v>46135.68820601852</v>
       </c>
       <c r="B242" t="inlineStr">
@@ -4300,7 +4312,7 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="1" t="n">
+      <c r="A243" s="2" t="n">
         <v>46135.86390046297</v>
       </c>
       <c r="B243" t="inlineStr">
@@ -4316,7 +4328,7 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="1" t="n">
+      <c r="A244" s="2" t="n">
         <v>46136.02126157407</v>
       </c>
       <c r="B244" t="inlineStr">
@@ -4332,7 +4344,7 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="1" t="n">
+      <c r="A245" s="2" t="n">
         <v>46136.18943287037</v>
       </c>
       <c r="B245" t="inlineStr">
@@ -4348,7 +4360,7 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="1" t="n">
+      <c r="A246" s="2" t="n">
         <v>46136.35768518518</v>
       </c>
       <c r="B246" t="inlineStr">
@@ -4364,7 +4376,7 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="1" t="n">
+      <c r="A247" s="2" t="n">
         <v>46136.52224537037</v>
       </c>
       <c r="B247" t="inlineStr">
@@ -4380,7 +4392,7 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="1" t="n">
+      <c r="A248" s="2" t="n">
         <v>46136.6883912037</v>
       </c>
       <c r="B248" t="inlineStr">
@@ -4396,7 +4408,7 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="1" t="n">
+      <c r="A249" s="2" t="n">
         <v>46136.85456018519</v>
       </c>
       <c r="B249" t="inlineStr">
@@ -4412,7 +4424,7 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="1" t="n">
+      <c r="A250" s="2" t="n">
         <v>46137.0588425926</v>
       </c>
       <c r="B250" t="inlineStr">
@@ -4428,7 +4440,7 @@
       </c>
     </row>
     <row r="251">
-      <c r="A251" s="1" t="n">
+      <c r="A251" s="2" t="n">
         <v>46137.18950231482</v>
       </c>
       <c r="B251" t="inlineStr">
@@ -4444,7 +4456,7 @@
       </c>
     </row>
     <row r="252">
-      <c r="A252" s="1" t="n">
+      <c r="A252" s="2" t="n">
         <v>46137.36697916667</v>
       </c>
       <c r="B252" t="inlineStr">
@@ -4460,7 +4472,7 @@
       </c>
     </row>
     <row r="253">
-      <c r="A253" s="1" t="n">
+      <c r="A253" s="2" t="n">
         <v>46137.52636574074</v>
       </c>
       <c r="B253" t="inlineStr">
@@ -4476,7 +4488,7 @@
       </c>
     </row>
     <row r="254">
-      <c r="A254" s="1" t="n">
+      <c r="A254" s="2" t="n">
         <v>46137.68905092592</v>
       </c>
       <c r="B254" t="inlineStr">
@@ -4492,7 +4504,7 @@
       </c>
     </row>
     <row r="255">
-      <c r="A255" s="1" t="n">
+      <c r="A255" s="2" t="n">
         <v>46137.8555787037</v>
       </c>
       <c r="B255" t="inlineStr">
@@ -4508,7 +4520,7 @@
       </c>
     </row>
     <row r="256">
-      <c r="A256" s="1" t="n">
+      <c r="A256" s="2" t="n">
         <v>46138.08900462963</v>
       </c>
       <c r="B256" t="inlineStr">
@@ -4524,7 +4536,7 @@
       </c>
     </row>
     <row r="257">
-      <c r="A257" s="1" t="n">
+      <c r="A257" s="2" t="n">
         <v>46138.22342592593</v>
       </c>
       <c r="B257" t="inlineStr">
@@ -4540,7 +4552,7 @@
       </c>
     </row>
     <row r="258">
-      <c r="A258" s="1" t="n">
+      <c r="A258" s="2" t="n">
         <v>46138.35784722222</v>
       </c>
       <c r="B258" t="inlineStr">
@@ -4556,7 +4568,7 @@
       </c>
     </row>
     <row r="259">
-      <c r="A259" s="1" t="n">
+      <c r="A259" s="2" t="n">
         <v>46138.54626157408</v>
       </c>
       <c r="B259" t="inlineStr">
@@ -4572,7 +4584,7 @@
       </c>
     </row>
     <row r="260">
-      <c r="A260" s="1" t="n">
+      <c r="A260" s="2" t="n">
         <v>46138.69407407408</v>
       </c>
       <c r="B260" t="inlineStr">
@@ -4588,7 +4600,7 @@
       </c>
     </row>
     <row r="261">
-      <c r="A261" s="1" t="n">
+      <c r="A261" s="2" t="n">
         <v>46138.85946759259</v>
       </c>
       <c r="B261" t="inlineStr">
@@ -4604,7 +4616,7 @@
       </c>
     </row>
     <row r="262">
-      <c r="A262" s="1" t="n">
+      <c r="A262" s="2" t="n">
         <v>46139.04685185185</v>
       </c>
       <c r="B262" t="inlineStr">
@@ -4620,7 +4632,7 @@
       </c>
     </row>
     <row r="263">
-      <c r="A263" s="1" t="n">
+      <c r="A263" s="2" t="n">
         <v>46139.20314814815</v>
       </c>
       <c r="B263" t="inlineStr">
@@ -4636,7 +4648,7 @@
       </c>
     </row>
     <row r="264">
-      <c r="A264" s="1" t="n">
+      <c r="A264" s="2" t="n">
         <v>46139.35634259259</v>
       </c>
       <c r="B264" t="inlineStr">
@@ -4652,7 +4664,7 @@
       </c>
     </row>
     <row r="265">
-      <c r="A265" s="1" t="n">
+      <c r="A265" s="2" t="n">
         <v>46139.52431712963</v>
       </c>
       <c r="B265" t="inlineStr">
@@ -4668,7 +4680,7 @@
       </c>
     </row>
     <row r="266">
-      <c r="A266" s="1" t="n">
+      <c r="A266" s="2" t="n">
         <v>46139.69873842593</v>
       </c>
       <c r="B266" t="inlineStr">
@@ -4684,7 +4696,7 @@
       </c>
     </row>
     <row r="267">
-      <c r="A267" s="1" t="n">
+      <c r="A267" s="2" t="n">
         <v>46139.86931712963</v>
       </c>
       <c r="B267" t="inlineStr">
@@ -4700,7 +4712,7 @@
       </c>
     </row>
     <row r="268">
-      <c r="A268" s="1" t="n">
+      <c r="A268" s="2" t="n">
         <v>46140.02158564814</v>
       </c>
       <c r="B268" t="inlineStr">
@@ -4716,7 +4728,7 @@
       </c>
     </row>
     <row r="269">
-      <c r="A269" s="1" t="n">
+      <c r="A269" s="2" t="n">
         <v>46140.19370370371</v>
       </c>
       <c r="B269" t="inlineStr">
@@ -4732,7 +4744,7 @@
       </c>
     </row>
     <row r="270">
-      <c r="A270" s="1" t="n">
+      <c r="A270" s="2" t="n">
         <v>46140.35989583333</v>
       </c>
       <c r="B270" t="inlineStr">
@@ -4748,7 +4760,7 @@
       </c>
     </row>
     <row r="271">
-      <c r="A271" s="1" t="n">
+      <c r="A271" s="2" t="n">
         <v>46140.52547453704</v>
       </c>
       <c r="B271" t="inlineStr">
@@ -4764,7 +4776,7 @@
       </c>
     </row>
     <row r="272">
-      <c r="A272" s="1" t="n">
+      <c r="A272" s="2" t="n">
         <v>46140.69204861111</v>
       </c>
       <c r="B272" t="inlineStr">
@@ -4780,7 +4792,7 @@
       </c>
     </row>
     <row r="273">
-      <c r="A273" s="1" t="n">
+      <c r="A273" s="2" t="n">
         <v>46140.85797453704</v>
       </c>
       <c r="B273" t="inlineStr">
@@ -4796,7 +4808,7 @@
       </c>
     </row>
     <row r="274">
-      <c r="A274" s="1" t="n">
+      <c r="A274" s="2" t="n">
         <v>46141.08907407407</v>
       </c>
       <c r="B274" t="inlineStr">
@@ -4812,7 +4824,7 @@
       </c>
     </row>
     <row r="275">
-      <c r="A275" s="1" t="n">
+      <c r="A275" s="2" t="n">
         <v>46141.19405092593</v>
       </c>
       <c r="B275" t="inlineStr">
@@ -4828,7 +4840,7 @@
       </c>
     </row>
     <row r="276">
-      <c r="A276" s="1" t="n">
+      <c r="A276" s="2" t="n">
         <v>46141.37282407407</v>
       </c>
       <c r="B276" t="inlineStr">
@@ -4844,7 +4856,7 @@
       </c>
     </row>
     <row r="277">
-      <c r="A277" s="1" t="n">
+      <c r="A277" s="2" t="n">
         <v>46141.52434027778</v>
       </c>
       <c r="B277" t="inlineStr">
@@ -4860,7 +4872,7 @@
       </c>
     </row>
     <row r="278">
-      <c r="A278" s="1" t="n">
+      <c r="A278" s="2" t="n">
         <v>46141.69369212963</v>
       </c>
       <c r="B278" t="inlineStr">
@@ -4876,7 +4888,7 @@
       </c>
     </row>
     <row r="279">
-      <c r="A279" s="1" t="n">
+      <c r="A279" s="2" t="n">
         <v>46141.85452546296</v>
       </c>
       <c r="B279" t="inlineStr">
@@ -4892,7 +4904,7 @@
       </c>
     </row>
     <row r="280">
-      <c r="A280" s="1" t="n">
+      <c r="A280" s="2" t="n">
         <v>46142.09556712963</v>
       </c>
       <c r="B280" t="inlineStr">
@@ -4908,7 +4920,7 @@
       </c>
     </row>
     <row r="281">
-      <c r="A281" s="1" t="n">
+      <c r="A281" s="2" t="n">
         <v>46142.22015046296</v>
       </c>
       <c r="B281" t="inlineStr">
@@ -4924,7 +4936,7 @@
       </c>
     </row>
     <row r="282">
-      <c r="A282" s="1" t="n">
+      <c r="A282" s="2" t="n">
         <v>46142.35427083333</v>
       </c>
       <c r="B282" t="inlineStr">
@@ -4940,7 +4952,7 @@
       </c>
     </row>
     <row r="283">
-      <c r="A283" s="1" t="n">
+      <c r="A283" s="2" t="n">
         <v>46142.52810185185</v>
       </c>
       <c r="B283" t="inlineStr">
@@ -4956,7 +4968,7 @@
       </c>
     </row>
     <row r="284">
-      <c r="A284" s="1" t="n">
+      <c r="A284" s="2" t="n">
         <v>46142.70089120371</v>
       </c>
       <c r="B284" t="inlineStr">
@@ -4972,7 +4984,7 @@
       </c>
     </row>
     <row r="285">
-      <c r="A285" s="1" t="n">
+      <c r="A285" s="2" t="n">
         <v>46142.85965277778</v>
       </c>
       <c r="B285" t="inlineStr">
@@ -4988,7 +5000,7 @@
       </c>
     </row>
     <row r="286">
-      <c r="A286" s="1" t="n">
+      <c r="A286" s="2" t="n">
         <v>46143.02594907407</v>
       </c>
       <c r="B286" t="inlineStr">
@@ -5004,7 +5016,7 @@
       </c>
     </row>
     <row r="287">
-      <c r="A287" s="1" t="n">
+      <c r="A287" s="2" t="n">
         <v>46143.20488425926</v>
       </c>
       <c r="B287" t="inlineStr">
@@ -5020,7 +5032,7 @@
       </c>
     </row>
     <row r="288">
-      <c r="A288" s="1" t="n">
+      <c r="A288" s="2" t="n">
         <v>46143.35506944444</v>
       </c>
       <c r="B288" t="inlineStr">
@@ -5036,7 +5048,7 @@
       </c>
     </row>
     <row r="289">
-      <c r="A289" s="1" t="n">
+      <c r="A289" s="2" t="n">
         <v>46143.52101851852</v>
       </c>
       <c r="B289" t="inlineStr">
@@ -5052,7 +5064,7 @@
       </c>
     </row>
     <row r="290">
-      <c r="A290" s="1" t="n">
+      <c r="A290" s="2" t="n">
         <v>46143.69318287037</v>
       </c>
       <c r="B290" t="inlineStr">
@@ -5068,7 +5080,7 @@
       </c>
     </row>
     <row r="291">
-      <c r="A291" s="1" t="n">
+      <c r="A291" s="2" t="n">
         <v>46143.86835648148</v>
       </c>
       <c r="B291" t="inlineStr">
@@ -5084,7 +5096,7 @@
       </c>
     </row>
     <row r="292">
-      <c r="A292" s="1" t="n">
+      <c r="A292" s="2" t="n">
         <v>46144.02177083334</v>
       </c>
       <c r="B292" t="inlineStr">
@@ -5100,7 +5112,7 @@
       </c>
     </row>
     <row r="293">
-      <c r="A293" s="1" t="n">
+      <c r="A293" s="2" t="n">
         <v>46144.18803240741</v>
       </c>
       <c r="B293" t="inlineStr">
@@ -5116,7 +5128,7 @@
       </c>
     </row>
     <row r="294">
-      <c r="A294" s="1" t="n">
+      <c r="A294" s="2" t="n">
         <v>46144.35827546296</v>
       </c>
       <c r="B294" t="inlineStr">
@@ -5132,7 +5144,7 @@
       </c>
     </row>
     <row r="295">
-      <c r="A295" s="1" t="n">
+      <c r="A295" s="2" t="n">
         <v>46144.52101851852</v>
       </c>
       <c r="B295" t="inlineStr">
@@ -5148,7 +5160,7 @@
       </c>
     </row>
     <row r="296">
-      <c r="A296" s="1" t="n">
+      <c r="A296" s="2" t="n">
         <v>46144.69450231481</v>
       </c>
       <c r="B296" t="inlineStr">
@@ -5164,7 +5176,7 @@
       </c>
     </row>
     <row r="297">
-      <c r="A297" s="1" t="n">
+      <c r="A297" s="2" t="n">
         <v>46144.85748842593</v>
       </c>
       <c r="B297" t="inlineStr">
@@ -5180,7 +5192,7 @@
       </c>
     </row>
     <row r="298">
-      <c r="A298" s="1" t="n">
+      <c r="A298" s="2" t="n">
         <v>46145.06841435185</v>
       </c>
       <c r="B298" t="inlineStr">
@@ -5196,7 +5208,7 @@
       </c>
     </row>
     <row r="299">
-      <c r="A299" s="1" t="n">
+      <c r="A299" s="2" t="n">
         <v>46145.20671296296</v>
       </c>
       <c r="B299" t="inlineStr">
@@ -5212,7 +5224,7 @@
       </c>
     </row>
     <row r="300">
-      <c r="A300" s="1" t="n">
+      <c r="A300" s="2" t="n">
         <v>46145.35491898148</v>
       </c>
       <c r="B300" t="inlineStr">
@@ -5228,7 +5240,7 @@
       </c>
     </row>
     <row r="301">
-      <c r="A301" s="1" t="n">
+      <c r="A301" s="2" t="n">
         <v>46145.52814814815</v>
       </c>
       <c r="B301" t="inlineStr">
@@ -5244,7 +5256,7 @@
       </c>
     </row>
     <row r="302">
-      <c r="A302" s="1" t="n">
+      <c r="A302" s="2" t="n">
         <v>46145.69175925926</v>
       </c>
       <c r="B302" t="inlineStr">
@@ -5260,7 +5272,7 @@
       </c>
     </row>
     <row r="303">
-      <c r="A303" s="1" t="n">
+      <c r="A303" s="2" t="n">
         <v>46145.85527777778</v>
       </c>
       <c r="B303" t="inlineStr">
@@ -5276,7 +5288,7 @@
       </c>
     </row>
     <row r="304">
-      <c r="A304" s="1" t="n">
+      <c r="A304" s="2" t="n">
         <v>46146.09436342592</v>
       </c>
       <c r="B304" t="inlineStr">
@@ -5292,7 +5304,7 @@
       </c>
     </row>
     <row r="305">
-      <c r="A305" s="1" t="n">
+      <c r="A305" s="2" t="n">
         <v>46146.21984953704</v>
       </c>
       <c r="B305" t="inlineStr">
@@ -5308,7 +5320,7 @@
       </c>
     </row>
     <row r="306">
-      <c r="A306" s="1" t="n">
+      <c r="A306" s="2" t="n">
         <v>46116.3550925926</v>
       </c>
       <c r="B306" t="inlineStr">
@@ -5324,7 +5336,7 @@
       </c>
     </row>
     <row r="307">
-      <c r="A307" s="1" t="n">
+      <c r="A307" s="2" t="n">
         <v>46116.52167824074</v>
       </c>
       <c r="B307" t="inlineStr">
@@ -5340,7 +5352,7 @@
       </c>
     </row>
     <row r="308">
-      <c r="A308" s="1" t="n">
+      <c r="A308" s="2" t="n">
         <v>46116.69474537037</v>
       </c>
       <c r="B308" t="inlineStr">
@@ -5356,7 +5368,7 @@
       </c>
     </row>
     <row r="309">
-      <c r="A309" s="1" t="n">
+      <c r="A309" s="2" t="n">
         <v>46116.85944444445</v>
       </c>
       <c r="B309" t="inlineStr">
@@ -5372,7 +5384,7 @@
       </c>
     </row>
     <row r="310">
-      <c r="A310" s="1" t="n">
+      <c r="A310" s="2" t="n">
         <v>46117.03664351852</v>
       </c>
       <c r="B310" t="inlineStr">
@@ -5388,7 +5400,7 @@
       </c>
     </row>
     <row r="311">
-      <c r="A311" s="1" t="n">
+      <c r="A311" s="2" t="n">
         <v>46117.24065972222</v>
       </c>
       <c r="B311" t="inlineStr">
@@ -5404,7 +5416,7 @@
       </c>
     </row>
     <row r="312">
-      <c r="A312" s="1" t="n">
+      <c r="A312" s="2" t="n">
         <v>46117.36049768519</v>
       </c>
       <c r="B312" t="inlineStr">
@@ -5420,7 +5432,7 @@
       </c>
     </row>
     <row r="313">
-      <c r="A313" s="1" t="n">
+      <c r="A313" s="2" t="n">
         <v>46117.52633101852</v>
       </c>
       <c r="B313" t="inlineStr">
@@ -5436,7 +5448,7 @@
       </c>
     </row>
     <row r="314">
-      <c r="A314" s="1" t="n">
+      <c r="A314" s="2" t="n">
         <v>46117.69008101852</v>
       </c>
       <c r="B314" t="inlineStr">
@@ -5452,7 +5464,7 @@
       </c>
     </row>
     <row r="315">
-      <c r="A315" s="1" t="n">
+      <c r="A315" s="2" t="n">
         <v>46117.87108796297</v>
       </c>
       <c r="B315" t="inlineStr">
@@ -5468,7 +5480,7 @@
       </c>
     </row>
     <row r="316">
-      <c r="A316" s="1" t="n">
+      <c r="A316" s="2" t="n">
         <v>46118.0265625</v>
       </c>
       <c r="B316" t="inlineStr">
@@ -5484,7 +5496,7 @@
       </c>
     </row>
     <row r="317">
-      <c r="A317" s="1" t="n">
+      <c r="A317" s="2" t="n">
         <v>46118.19368055555</v>
       </c>
       <c r="B317" t="inlineStr">
@@ -5500,7 +5512,7 @@
       </c>
     </row>
     <row r="318">
-      <c r="A318" s="1" t="n">
+      <c r="A318" s="2" t="n">
         <v>46118.36050925926</v>
       </c>
       <c r="B318" t="inlineStr">
@@ -5516,7 +5528,7 @@
       </c>
     </row>
     <row r="319">
-      <c r="A319" s="1" t="n">
+      <c r="A319" s="2" t="n">
         <v>46118.52253472222</v>
       </c>
       <c r="B319" t="inlineStr">
@@ -5532,7 +5544,7 @@
       </c>
     </row>
     <row r="320">
-      <c r="A320" s="1" t="n">
+      <c r="A320" s="2" t="n">
         <v>46118.68907407407</v>
       </c>
       <c r="B320" t="inlineStr">
@@ -5548,7 +5560,7 @@
       </c>
     </row>
     <row r="321">
-      <c r="A321" s="1" t="n">
+      <c r="A321" s="2" t="n">
         <v>46118.8552662037</v>
       </c>
       <c r="B321" t="inlineStr">
@@ -5564,7 +5576,7 @@
       </c>
     </row>
     <row r="322">
-      <c r="A322" s="1" t="n">
+      <c r="A322" s="2" t="n">
         <v>46119.02732638889</v>
       </c>
       <c r="B322" t="inlineStr">
@@ -5580,7 +5592,7 @@
       </c>
     </row>
     <row r="323">
-      <c r="A323" s="1" t="n">
+      <c r="A323" s="2" t="n">
         <v>46120.18833333333</v>
       </c>
       <c r="B323" t="inlineStr">
@@ -5596,7 +5608,7 @@
       </c>
     </row>
     <row r="324">
-      <c r="A324" s="1" t="n">
+      <c r="A324" s="2" t="n">
         <v>46120.52369212963</v>
       </c>
       <c r="B324" t="inlineStr">
@@ -5612,7 +5624,7 @@
       </c>
     </row>
     <row r="325">
-      <c r="A325" s="1" t="n">
+      <c r="A325" s="2" t="n">
         <v>46120.69190972222</v>
       </c>
       <c r="B325" t="inlineStr">
@@ -5628,7 +5640,7 @@
       </c>
     </row>
     <row r="326">
-      <c r="A326" s="1" t="n">
+      <c r="A326" s="2" t="n">
         <v>46120.85443287037</v>
       </c>
       <c r="B326" t="inlineStr">
@@ -5644,7 +5656,7 @@
       </c>
     </row>
     <row r="327">
-      <c r="A327" s="1" t="n">
+      <c r="A327" s="2" t="n">
         <v>46124.39263888889</v>
       </c>
       <c r="B327" t="inlineStr">
@@ -5660,7 +5672,7 @@
       </c>
     </row>
     <row r="328">
-      <c r="A328" s="1" t="n">
+      <c r="A328" s="2" t="n">
         <v>46124.52407407408</v>
       </c>
       <c r="B328" t="inlineStr">
@@ -5676,7 +5688,7 @@
       </c>
     </row>
     <row r="329">
-      <c r="A329" s="1" t="n">
+      <c r="A329" s="2" t="n">
         <v>46124.69166666667</v>
       </c>
       <c r="B329" t="inlineStr">
@@ -5692,7 +5704,7 @@
       </c>
     </row>
     <row r="330">
-      <c r="A330" s="1" t="n">
+      <c r="A330" s="2" t="n">
         <v>46124.85614583334</v>
       </c>
       <c r="B330" t="inlineStr">
@@ -5708,7 +5720,7 @@
       </c>
     </row>
     <row r="331">
-      <c r="A331" s="1" t="n">
+      <c r="A331" s="2" t="n">
         <v>46125.07673611111</v>
       </c>
       <c r="B331" t="inlineStr">
@@ -5724,7 +5736,7 @@
       </c>
     </row>
     <row r="332">
-      <c r="A332" s="1" t="n">
+      <c r="A332" s="2" t="n">
         <v>46125.18878472222</v>
       </c>
       <c r="B332" t="inlineStr">
@@ -5740,7 +5752,7 @@
       </c>
     </row>
     <row r="333">
-      <c r="A333" s="1" t="n">
+      <c r="A333" s="2" t="n">
         <v>46125.37304398148</v>
       </c>
       <c r="B333" t="inlineStr">
@@ -5756,7 +5768,7 @@
       </c>
     </row>
     <row r="334">
-      <c r="A334" s="1" t="n">
+      <c r="A334" s="2" t="n">
         <v>46125.52486111111</v>
       </c>
       <c r="B334" t="inlineStr">
@@ -5772,7 +5784,7 @@
       </c>
     </row>
     <row r="335">
-      <c r="A335" s="1" t="n">
+      <c r="A335" s="2" t="n">
         <v>46125.69287037037</v>
       </c>
       <c r="B335" t="inlineStr">
@@ -5788,7 +5800,7 @@
       </c>
     </row>
     <row r="336">
-      <c r="A336" s="1" t="n">
+      <c r="A336" s="2" t="n">
         <v>46125.85716435185</v>
       </c>
       <c r="B336" t="inlineStr">
@@ -5804,7 +5816,7 @@
       </c>
     </row>
     <row r="337">
-      <c r="A337" s="1" t="n">
+      <c r="A337" s="2" t="n">
         <v>46126.03134259259</v>
       </c>
       <c r="B337" t="inlineStr">
@@ -5820,7 +5832,7 @@
       </c>
     </row>
     <row r="338">
-      <c r="A338" s="1" t="n">
+      <c r="A338" s="2" t="n">
         <v>46126.21274305556</v>
       </c>
       <c r="B338" t="inlineStr">
@@ -5836,7 +5848,7 @@
       </c>
     </row>
     <row r="339">
-      <c r="A339" s="1" t="n">
+      <c r="A339" s="2" t="n">
         <v>46126.35861111111</v>
       </c>
       <c r="B339" t="inlineStr">
@@ -5852,7 +5864,7 @@
       </c>
     </row>
     <row r="340">
-      <c r="A340" s="1" t="n">
+      <c r="A340" s="2" t="n">
         <v>46126.53461805556</v>
       </c>
       <c r="B340" t="inlineStr">
@@ -5868,7 +5880,7 @@
       </c>
     </row>
     <row r="341">
-      <c r="A341" s="1" t="n">
+      <c r="A341" s="2" t="n">
         <v>46126.70118055555</v>
       </c>
       <c r="B341" t="inlineStr">
@@ -5884,7 +5896,7 @@
       </c>
     </row>
     <row r="342">
-      <c r="A342" s="1" t="n">
+      <c r="A342" s="2" t="n">
         <v>46126.87692129629</v>
       </c>
       <c r="B342" t="inlineStr">
@@ -5900,7 +5912,7 @@
       </c>
     </row>
     <row r="343">
-      <c r="A343" s="1" t="n">
+      <c r="A343" s="2" t="n">
         <v>46127.02172453704</v>
       </c>
       <c r="B343" t="inlineStr">
@@ -5916,7 +5928,7 @@
       </c>
     </row>
     <row r="344">
-      <c r="A344" s="1" t="n">
+      <c r="A344" s="2" t="n">
         <v>46127.20758101852</v>
       </c>
       <c r="B344" t="inlineStr">
@@ -5932,7 +5944,7 @@
       </c>
     </row>
     <row r="345">
-      <c r="A345" s="1" t="n">
+      <c r="A345" s="2" t="n">
         <v>46127.35572916667</v>
       </c>
       <c r="B345" t="inlineStr">
@@ -5948,7 +5960,7 @@
       </c>
     </row>
     <row r="346">
-      <c r="A346" s="1" t="n">
+      <c r="A346" s="2" t="n">
         <v>46127.53050925926</v>
       </c>
       <c r="B346" t="inlineStr">
@@ -5964,7 +5976,7 @@
       </c>
     </row>
     <row r="347">
-      <c r="A347" s="1" t="n">
+      <c r="A347" s="2" t="n">
         <v>46127.69168981481</v>
       </c>
       <c r="B347" t="inlineStr">
@@ -5980,7 +5992,7 @@
       </c>
     </row>
     <row r="348">
-      <c r="A348" s="1" t="n">
+      <c r="A348" s="2" t="n">
         <v>46127.85546296297</v>
       </c>
       <c r="B348" t="inlineStr">
@@ -5996,7 +6008,7 @@
       </c>
     </row>
     <row r="349">
-      <c r="A349" s="1" t="n">
+      <c r="A349" s="2" t="n">
         <v>46128.04122685185</v>
       </c>
       <c r="B349" t="inlineStr">
@@ -6012,7 +6024,7 @@
       </c>
     </row>
     <row r="350">
-      <c r="A350" s="1" t="n">
+      <c r="A350" s="2" t="n">
         <v>46128.19846064815</v>
       </c>
       <c r="B350" t="inlineStr">
@@ -6028,7 +6040,7 @@
       </c>
     </row>
     <row r="351">
-      <c r="A351" s="1" t="n">
+      <c r="A351" s="2" t="n">
         <v>46128.3578125</v>
       </c>
       <c r="B351" t="inlineStr">
@@ -6044,7 +6056,7 @@
       </c>
     </row>
     <row r="352">
-      <c r="A352" s="1" t="n">
+      <c r="A352" s="2" t="n">
         <v>46128.52149305555</v>
       </c>
       <c r="B352" t="inlineStr">
@@ -6060,7 +6072,7 @@
       </c>
     </row>
     <row r="353">
-      <c r="A353" s="1" t="n">
+      <c r="A353" s="2" t="n">
         <v>46128.69186342593</v>
       </c>
       <c r="B353" t="inlineStr">
@@ -6076,7 +6088,7 @@
       </c>
     </row>
     <row r="354">
-      <c r="A354" s="1" t="n">
+      <c r="A354" s="2" t="n">
         <v>46128.85454861111</v>
       </c>
       <c r="B354" t="inlineStr">
@@ -6092,7 +6104,7 @@
       </c>
     </row>
     <row r="355">
-      <c r="A355" s="1" t="n">
+      <c r="A355" s="2" t="n">
         <v>46129.08709490741</v>
       </c>
       <c r="B355" t="inlineStr">
@@ -6108,7 +6120,7 @@
       </c>
     </row>
     <row r="356">
-      <c r="A356" s="1" t="n">
+      <c r="A356" s="2" t="n">
         <v>46129.20550925926</v>
       </c>
       <c r="B356" t="inlineStr">
@@ -6124,7 +6136,7 @@
       </c>
     </row>
     <row r="357">
-      <c r="A357" s="1" t="n">
+      <c r="A357" s="2" t="n">
         <v>46129.36481481481</v>
       </c>
       <c r="B357" t="inlineStr">
@@ -6140,7 +6152,7 @@
       </c>
     </row>
     <row r="358">
-      <c r="A358" s="1" t="n">
+      <c r="A358" s="2" t="n">
         <v>46129.52703703703</v>
       </c>
       <c r="B358" t="inlineStr">
@@ -6156,7 +6168,7 @@
       </c>
     </row>
     <row r="359">
-      <c r="A359" s="1" t="n">
+      <c r="A359" s="2" t="n">
         <v>46129.69325231481</v>
       </c>
       <c r="B359" t="inlineStr">
@@ -6172,7 +6184,7 @@
       </c>
     </row>
     <row r="360">
-      <c r="A360" s="1" t="n">
+      <c r="A360" s="2" t="n">
         <v>46129.85914351852</v>
       </c>
       <c r="B360" t="inlineStr">
@@ -6188,7 +6200,7 @@
       </c>
     </row>
     <row r="361">
-      <c r="A361" s="1" t="n">
+      <c r="A361" s="2" t="n">
         <v>46130.09744212963</v>
       </c>
       <c r="B361" t="inlineStr">
@@ -6204,7 +6216,7 @@
       </c>
     </row>
     <row r="362">
-      <c r="A362" s="1" t="n">
+      <c r="A362" s="2" t="n">
         <v>46130.19385416667</v>
       </c>
       <c r="B362" t="inlineStr">
@@ -6220,7 +6232,7 @@
       </c>
     </row>
     <row r="363">
-      <c r="A363" s="1" t="n">
+      <c r="A363" s="2" t="n">
         <v>46130.35618055556</v>
       </c>
       <c r="B363" t="inlineStr">
@@ -6236,7 +6248,7 @@
       </c>
     </row>
     <row r="364">
-      <c r="A364" s="1" t="n">
+      <c r="A364" s="2" t="n">
         <v>46130.52403935185</v>
       </c>
       <c r="B364" t="inlineStr">
@@ -6252,7 +6264,7 @@
       </c>
     </row>
     <row r="365">
-      <c r="A365" s="1" t="n">
+      <c r="A365" s="2" t="n">
         <v>46130.68988425926</v>
       </c>
       <c r="B365" t="inlineStr">
@@ -6268,7 +6280,7 @@
       </c>
     </row>
     <row r="366">
-      <c r="A366" s="1" t="n">
+      <c r="A366" s="2" t="n">
         <v>46131.02777777778</v>
       </c>
       <c r="B366" t="inlineStr">
@@ -6284,7 +6296,7 @@
       </c>
     </row>
     <row r="367">
-      <c r="A367" s="1" t="n">
+      <c r="A367" s="2" t="n">
         <v>46131.19017361111</v>
       </c>
       <c r="B367" t="inlineStr">
@@ -6300,7 +6312,7 @@
       </c>
     </row>
     <row r="368">
-      <c r="A368" s="1" t="n">
+      <c r="A368" s="2" t="n">
         <v>46131.35472222222</v>
       </c>
       <c r="B368" t="inlineStr">
@@ -6316,7 +6328,7 @@
       </c>
     </row>
     <row r="369">
-      <c r="A369" s="1" t="n">
+      <c r="A369" s="2" t="n">
         <v>46131.52929398148</v>
       </c>
       <c r="B369" t="inlineStr">
@@ -6332,7 +6344,7 @@
       </c>
     </row>
     <row r="370">
-      <c r="A370" s="1" t="n">
+      <c r="A370" s="2" t="n">
         <v>46131.68760416667</v>
       </c>
       <c r="B370" t="inlineStr">
@@ -6348,7 +6360,7 @@
       </c>
     </row>
     <row r="371">
-      <c r="A371" s="1" t="n">
+      <c r="A371" s="2" t="n">
         <v>46131.8633912037</v>
       </c>
       <c r="B371" t="inlineStr">
@@ -6364,7 +6376,7 @@
       </c>
     </row>
     <row r="372">
-      <c r="A372" s="1" t="n">
+      <c r="A372" s="2" t="n">
         <v>46132.02103009259</v>
       </c>
       <c r="B372" t="inlineStr">
@@ -6380,7 +6392,7 @@
       </c>
     </row>
     <row r="373">
-      <c r="A373" s="1" t="n">
+      <c r="A373" s="2" t="n">
         <v>46132.19717592592</v>
       </c>
       <c r="B373" t="inlineStr">
@@ -6396,7 +6408,7 @@
       </c>
     </row>
     <row r="374">
-      <c r="A374" s="1" t="n">
+      <c r="A374" s="2" t="n">
         <v>46132.3584375</v>
       </c>
       <c r="B374" t="inlineStr">
@@ -6412,7 +6424,7 @@
       </c>
     </row>
     <row r="375">
-      <c r="A375" s="1" t="n">
+      <c r="A375" s="2" t="n">
         <v>46132.52159722222</v>
       </c>
       <c r="B375" t="inlineStr">
@@ -6428,7 +6440,7 @@
       </c>
     </row>
     <row r="376">
-      <c r="A376" s="1" t="n">
+      <c r="A376" s="2" t="n">
         <v>46132.69394675926</v>
       </c>
       <c r="B376" t="inlineStr">
@@ -6444,7 +6456,7 @@
       </c>
     </row>
     <row r="377">
-      <c r="A377" s="1" t="n">
+      <c r="A377" s="2" t="n">
         <v>46132.86247685185</v>
       </c>
       <c r="B377" t="inlineStr">
@@ -6460,7 +6472,7 @@
       </c>
     </row>
     <row r="378">
-      <c r="A378" s="1" t="n">
+      <c r="A378" s="2" t="n">
         <v>46133.07111111111</v>
       </c>
       <c r="B378" t="inlineStr">
@@ -6476,7 +6488,7 @@
       </c>
     </row>
     <row r="379">
-      <c r="A379" s="1" t="n">
+      <c r="A379" s="2" t="n">
         <v>46133.19524305555</v>
       </c>
       <c r="B379" t="inlineStr">
@@ -6492,7 +6504,7 @@
       </c>
     </row>
     <row r="380">
-      <c r="A380" s="1" t="n">
+      <c r="A380" s="2" t="n">
         <v>46133.36118055556</v>
       </c>
       <c r="B380" t="inlineStr">
@@ -6508,7 +6520,7 @@
       </c>
     </row>
     <row r="381">
-      <c r="A381" s="1" t="n">
+      <c r="A381" s="2" t="n">
         <v>46133.52528935186</v>
       </c>
       <c r="B381" t="inlineStr">
@@ -6524,7 +6536,7 @@
       </c>
     </row>
     <row r="382">
-      <c r="A382" s="1" t="n">
+      <c r="A382" s="2" t="n">
         <v>46133.69530092592</v>
       </c>
       <c r="B382" t="inlineStr">
@@ -6540,7 +6552,7 @@
       </c>
     </row>
     <row r="383">
-      <c r="A383" s="1" t="n">
+      <c r="A383" s="2" t="n">
         <v>46133.85505787037</v>
       </c>
       <c r="B383" t="inlineStr">
@@ -6556,7 +6568,7 @@
       </c>
     </row>
     <row r="384">
-      <c r="A384" s="1" t="n">
+      <c r="A384" s="2" t="n">
         <v>46134.09811342593</v>
       </c>
       <c r="B384" t="inlineStr">
@@ -6572,7 +6584,7 @@
       </c>
     </row>
     <row r="385">
-      <c r="A385" s="1" t="n">
+      <c r="A385" s="2" t="n">
         <v>46134.21712962963</v>
       </c>
       <c r="B385" t="inlineStr">
@@ -6588,7 +6600,7 @@
       </c>
     </row>
     <row r="386">
-      <c r="A386" s="1" t="n">
+      <c r="A386" s="2" t="n">
         <v>46134.35688657407</v>
       </c>
       <c r="B386" t="inlineStr">
@@ -6604,7 +6616,7 @@
       </c>
     </row>
     <row r="387">
-      <c r="A387" s="1" t="n">
+      <c r="A387" s="2" t="n">
         <v>46134.52453703704</v>
       </c>
       <c r="B387" t="inlineStr">
@@ -6620,7 +6632,7 @@
       </c>
     </row>
     <row r="388">
-      <c r="A388" s="1" t="n">
+      <c r="A388" s="2" t="n">
         <v>46134.72311342593</v>
       </c>
       <c r="B388" t="inlineStr">
@@ -6636,7 +6648,7 @@
       </c>
     </row>
     <row r="389">
-      <c r="A389" s="1" t="n">
+      <c r="A389" s="2" t="n">
         <v>46134.85905092592</v>
       </c>
       <c r="B389" t="inlineStr">
@@ -6652,7 +6664,7 @@
       </c>
     </row>
     <row r="390">
-      <c r="A390" s="1" t="n">
+      <c r="A390" s="2" t="n">
         <v>46135.02693287037</v>
       </c>
       <c r="B390" t="inlineStr">
@@ -6668,7 +6680,7 @@
       </c>
     </row>
     <row r="391">
-      <c r="A391" s="1" t="n">
+      <c r="A391" s="2" t="n">
         <v>46135.19215277778</v>
       </c>
       <c r="B391" t="inlineStr">
@@ -6684,7 +6696,7 @@
       </c>
     </row>
     <row r="392">
-      <c r="A392" s="1" t="n">
+      <c r="A392" s="2" t="n">
         <v>46135.3603125</v>
       </c>
       <c r="B392" t="inlineStr">
@@ -6700,7 +6712,7 @@
       </c>
     </row>
     <row r="393">
-      <c r="A393" s="1" t="n">
+      <c r="A393" s="2" t="n">
         <v>46135.53359953704</v>
       </c>
       <c r="B393" t="inlineStr">
@@ -6716,7 +6728,7 @@
       </c>
     </row>
     <row r="394">
-      <c r="A394" s="1" t="n">
+      <c r="A394" s="2" t="n">
         <v>46135.68820601852</v>
       </c>
       <c r="B394" t="inlineStr">
@@ -6732,7 +6744,7 @@
       </c>
     </row>
     <row r="395">
-      <c r="A395" s="1" t="n">
+      <c r="A395" s="2" t="n">
         <v>46135.86390046297</v>
       </c>
       <c r="B395" t="inlineStr">
@@ -6748,7 +6760,7 @@
       </c>
     </row>
     <row r="396">
-      <c r="A396" s="1" t="n">
+      <c r="A396" s="2" t="n">
         <v>46136.02126157407</v>
       </c>
       <c r="B396" t="inlineStr">
@@ -6764,7 +6776,7 @@
       </c>
     </row>
     <row r="397">
-      <c r="A397" s="1" t="n">
+      <c r="A397" s="2" t="n">
         <v>46136.18943287037</v>
       </c>
       <c r="B397" t="inlineStr">
@@ -6780,7 +6792,7 @@
       </c>
     </row>
     <row r="398">
-      <c r="A398" s="1" t="n">
+      <c r="A398" s="2" t="n">
         <v>46136.35768518518</v>
       </c>
       <c r="B398" t="inlineStr">
@@ -6796,7 +6808,7 @@
       </c>
     </row>
     <row r="399">
-      <c r="A399" s="1" t="n">
+      <c r="A399" s="2" t="n">
         <v>46136.52224537037</v>
       </c>
       <c r="B399" t="inlineStr">
@@ -6812,7 +6824,7 @@
       </c>
     </row>
     <row r="400">
-      <c r="A400" s="1" t="n">
+      <c r="A400" s="2" t="n">
         <v>46136.6883912037</v>
       </c>
       <c r="B400" t="inlineStr">
@@ -6828,7 +6840,7 @@
       </c>
     </row>
     <row r="401">
-      <c r="A401" s="1" t="n">
+      <c r="A401" s="2" t="n">
         <v>46136.85456018519</v>
       </c>
       <c r="B401" t="inlineStr">
@@ -6844,7 +6856,7 @@
       </c>
     </row>
     <row r="402">
-      <c r="A402" s="1" t="n">
+      <c r="A402" s="2" t="n">
         <v>46137.0588425926</v>
       </c>
       <c r="B402" t="inlineStr">
@@ -6860,7 +6872,7 @@
       </c>
     </row>
     <row r="403">
-      <c r="A403" s="1" t="n">
+      <c r="A403" s="2" t="n">
         <v>46137.18950231482</v>
       </c>
       <c r="B403" t="inlineStr">
@@ -6876,7 +6888,7 @@
       </c>
     </row>
     <row r="404">
-      <c r="A404" s="1" t="n">
+      <c r="A404" s="2" t="n">
         <v>46137.36697916667</v>
       </c>
       <c r="B404" t="inlineStr">
@@ -6892,7 +6904,7 @@
       </c>
     </row>
     <row r="405">
-      <c r="A405" s="1" t="n">
+      <c r="A405" s="2" t="n">
         <v>46137.52636574074</v>
       </c>
       <c r="B405" t="inlineStr">
@@ -6908,7 +6920,7 @@
       </c>
     </row>
     <row r="406">
-      <c r="A406" s="1" t="n">
+      <c r="A406" s="2" t="n">
         <v>46137.68905092592</v>
       </c>
       <c r="B406" t="inlineStr">
@@ -6924,7 +6936,7 @@
       </c>
     </row>
     <row r="407">
-      <c r="A407" s="1" t="n">
+      <c r="A407" s="2" t="n">
         <v>46137.8555787037</v>
       </c>
       <c r="B407" t="inlineStr">
@@ -6940,7 +6952,7 @@
       </c>
     </row>
     <row r="408">
-      <c r="A408" s="1" t="n">
+      <c r="A408" s="2" t="n">
         <v>46138.08900462963</v>
       </c>
       <c r="B408" t="inlineStr">
@@ -6956,7 +6968,7 @@
       </c>
     </row>
     <row r="409">
-      <c r="A409" s="1" t="n">
+      <c r="A409" s="2" t="n">
         <v>46138.22342592593</v>
       </c>
       <c r="B409" t="inlineStr">
@@ -6972,7 +6984,7 @@
       </c>
     </row>
     <row r="410">
-      <c r="A410" s="1" t="n">
+      <c r="A410" s="2" t="n">
         <v>46138.35784722222</v>
       </c>
       <c r="B410" t="inlineStr">
@@ -6988,7 +7000,7 @@
       </c>
     </row>
     <row r="411">
-      <c r="A411" s="1" t="n">
+      <c r="A411" s="2" t="n">
         <v>46138.54626157408</v>
       </c>
       <c r="B411" t="inlineStr">
@@ -7004,7 +7016,7 @@
       </c>
     </row>
     <row r="412">
-      <c r="A412" s="1" t="n">
+      <c r="A412" s="2" t="n">
         <v>46138.69407407408</v>
       </c>
       <c r="B412" t="inlineStr">
@@ -7020,7 +7032,7 @@
       </c>
     </row>
     <row r="413">
-      <c r="A413" s="1" t="n">
+      <c r="A413" s="2" t="n">
         <v>46138.85946759259</v>
       </c>
       <c r="B413" t="inlineStr">
@@ -7036,7 +7048,7 @@
       </c>
     </row>
     <row r="414">
-      <c r="A414" s="1" t="n">
+      <c r="A414" s="2" t="n">
         <v>46139.04685185185</v>
       </c>
       <c r="B414" t="inlineStr">
@@ -7052,7 +7064,7 @@
       </c>
     </row>
     <row r="415">
-      <c r="A415" s="1" t="n">
+      <c r="A415" s="2" t="n">
         <v>46139.20314814815</v>
       </c>
       <c r="B415" t="inlineStr">
@@ -7068,7 +7080,7 @@
       </c>
     </row>
     <row r="416">
-      <c r="A416" s="1" t="n">
+      <c r="A416" s="2" t="n">
         <v>46139.35634259259</v>
       </c>
       <c r="B416" t="inlineStr">
@@ -7084,7 +7096,7 @@
       </c>
     </row>
     <row r="417">
-      <c r="A417" s="1" t="n">
+      <c r="A417" s="2" t="n">
         <v>46139.52431712963</v>
       </c>
       <c r="B417" t="inlineStr">
@@ -7100,7 +7112,7 @@
       </c>
     </row>
     <row r="418">
-      <c r="A418" s="1" t="n">
+      <c r="A418" s="2" t="n">
         <v>46139.69873842593</v>
       </c>
       <c r="B418" t="inlineStr">
@@ -7116,7 +7128,7 @@
       </c>
     </row>
     <row r="419">
-      <c r="A419" s="1" t="n">
+      <c r="A419" s="2" t="n">
         <v>46139.86931712963</v>
       </c>
       <c r="B419" t="inlineStr">
@@ -7132,7 +7144,7 @@
       </c>
     </row>
     <row r="420">
-      <c r="A420" s="1" t="n">
+      <c r="A420" s="2" t="n">
         <v>46140.02158564814</v>
       </c>
       <c r="B420" t="inlineStr">
@@ -7148,7 +7160,7 @@
       </c>
     </row>
     <row r="421">
-      <c r="A421" s="1" t="n">
+      <c r="A421" s="2" t="n">
         <v>46140.19370370371</v>
       </c>
       <c r="B421" t="inlineStr">
@@ -7164,7 +7176,7 @@
       </c>
     </row>
     <row r="422">
-      <c r="A422" s="1" t="n">
+      <c r="A422" s="2" t="n">
         <v>46140.35989583333</v>
       </c>
       <c r="B422" t="inlineStr">
@@ -7180,7 +7192,7 @@
       </c>
     </row>
     <row r="423">
-      <c r="A423" s="1" t="n">
+      <c r="A423" s="2" t="n">
         <v>46140.52547453704</v>
       </c>
       <c r="B423" t="inlineStr">
@@ -7196,7 +7208,7 @@
       </c>
     </row>
     <row r="424">
-      <c r="A424" s="1" t="n">
+      <c r="A424" s="2" t="n">
         <v>46140.69204861111</v>
       </c>
       <c r="B424" t="inlineStr">
@@ -7212,7 +7224,7 @@
       </c>
     </row>
     <row r="425">
-      <c r="A425" s="1" t="n">
+      <c r="A425" s="2" t="n">
         <v>46140.85797453704</v>
       </c>
       <c r="B425" t="inlineStr">
@@ -7228,7 +7240,7 @@
       </c>
     </row>
     <row r="426">
-      <c r="A426" s="1" t="n">
+      <c r="A426" s="2" t="n">
         <v>46141.08907407407</v>
       </c>
       <c r="B426" t="inlineStr">
@@ -7244,7 +7256,7 @@
       </c>
     </row>
     <row r="427">
-      <c r="A427" s="1" t="n">
+      <c r="A427" s="2" t="n">
         <v>46141.19405092593</v>
       </c>
       <c r="B427" t="inlineStr">
@@ -7260,7 +7272,7 @@
       </c>
     </row>
     <row r="428">
-      <c r="A428" s="1" t="n">
+      <c r="A428" s="2" t="n">
         <v>46141.37282407407</v>
       </c>
       <c r="B428" t="inlineStr">
@@ -7276,7 +7288,7 @@
       </c>
     </row>
     <row r="429">
-      <c r="A429" s="1" t="n">
+      <c r="A429" s="2" t="n">
         <v>46141.52434027778</v>
       </c>
       <c r="B429" t="inlineStr">
@@ -7292,7 +7304,7 @@
       </c>
     </row>
     <row r="430">
-      <c r="A430" s="1" t="n">
+      <c r="A430" s="2" t="n">
         <v>46141.69369212963</v>
       </c>
       <c r="B430" t="inlineStr">
@@ -7308,7 +7320,7 @@
       </c>
     </row>
     <row r="431">
-      <c r="A431" s="1" t="n">
+      <c r="A431" s="2" t="n">
         <v>46141.85452546296</v>
       </c>
       <c r="B431" t="inlineStr">
@@ -7324,7 +7336,7 @@
       </c>
     </row>
     <row r="432">
-      <c r="A432" s="1" t="n">
+      <c r="A432" s="2" t="n">
         <v>46142.09556712963</v>
       </c>
       <c r="B432" t="inlineStr">
@@ -7340,7 +7352,7 @@
       </c>
     </row>
     <row r="433">
-      <c r="A433" s="1" t="n">
+      <c r="A433" s="2" t="n">
         <v>46142.22015046296</v>
       </c>
       <c r="B433" t="inlineStr">
@@ -7356,7 +7368,7 @@
       </c>
     </row>
     <row r="434">
-      <c r="A434" s="1" t="n">
+      <c r="A434" s="2" t="n">
         <v>46142.35427083333</v>
       </c>
       <c r="B434" t="inlineStr">
@@ -7372,7 +7384,7 @@
       </c>
     </row>
     <row r="435">
-      <c r="A435" s="1" t="n">
+      <c r="A435" s="2" t="n">
         <v>46142.52810185185</v>
       </c>
       <c r="B435" t="inlineStr">
@@ -7388,7 +7400,7 @@
       </c>
     </row>
     <row r="436">
-      <c r="A436" s="1" t="n">
+      <c r="A436" s="2" t="n">
         <v>46142.70089120371</v>
       </c>
       <c r="B436" t="inlineStr">
@@ -7404,7 +7416,7 @@
       </c>
     </row>
     <row r="437">
-      <c r="A437" s="1" t="n">
+      <c r="A437" s="2" t="n">
         <v>46142.85965277778</v>
       </c>
       <c r="B437" t="inlineStr">
@@ -7420,7 +7432,7 @@
       </c>
     </row>
     <row r="438">
-      <c r="A438" s="1" t="n">
+      <c r="A438" s="2" t="n">
         <v>46143.02594907407</v>
       </c>
       <c r="B438" t="inlineStr">
@@ -7436,7 +7448,7 @@
       </c>
     </row>
     <row r="439">
-      <c r="A439" s="1" t="n">
+      <c r="A439" s="2" t="n">
         <v>46143.20488425926</v>
       </c>
       <c r="B439" t="inlineStr">
@@ -7452,7 +7464,7 @@
       </c>
     </row>
     <row r="440">
-      <c r="A440" s="1" t="n">
+      <c r="A440" s="2" t="n">
         <v>46143.35506944444</v>
       </c>
       <c r="B440" t="inlineStr">
@@ -7468,7 +7480,7 @@
       </c>
     </row>
     <row r="441">
-      <c r="A441" s="1" t="n">
+      <c r="A441" s="2" t="n">
         <v>46143.52101851852</v>
       </c>
       <c r="B441" t="inlineStr">
@@ -7484,7 +7496,7 @@
       </c>
     </row>
     <row r="442">
-      <c r="A442" s="1" t="n">
+      <c r="A442" s="2" t="n">
         <v>46143.69318287037</v>
       </c>
       <c r="B442" t="inlineStr">
@@ -7500,7 +7512,7 @@
       </c>
     </row>
     <row r="443">
-      <c r="A443" s="1" t="n">
+      <c r="A443" s="2" t="n">
         <v>46143.86835648148</v>
       </c>
       <c r="B443" t="inlineStr">
@@ -7516,7 +7528,7 @@
       </c>
     </row>
     <row r="444">
-      <c r="A444" s="1" t="n">
+      <c r="A444" s="2" t="n">
         <v>46144.02177083334</v>
       </c>
       <c r="B444" t="inlineStr">
@@ -7532,7 +7544,7 @@
       </c>
     </row>
     <row r="445">
-      <c r="A445" s="1" t="n">
+      <c r="A445" s="2" t="n">
         <v>46144.18803240741</v>
       </c>
       <c r="B445" t="inlineStr">
@@ -7548,7 +7560,7 @@
       </c>
     </row>
     <row r="446">
-      <c r="A446" s="1" t="n">
+      <c r="A446" s="2" t="n">
         <v>46144.35827546296</v>
       </c>
       <c r="B446" t="inlineStr">
@@ -7564,7 +7576,7 @@
       </c>
     </row>
     <row r="447">
-      <c r="A447" s="1" t="n">
+      <c r="A447" s="2" t="n">
         <v>46144.52101851852</v>
       </c>
       <c r="B447" t="inlineStr">
@@ -7580,7 +7592,7 @@
       </c>
     </row>
     <row r="448">
-      <c r="A448" s="1" t="n">
+      <c r="A448" s="2" t="n">
         <v>46144.69450231481</v>
       </c>
       <c r="B448" t="inlineStr">
@@ -7596,7 +7608,7 @@
       </c>
     </row>
     <row r="449">
-      <c r="A449" s="1" t="n">
+      <c r="A449" s="2" t="n">
         <v>46144.85748842593</v>
       </c>
       <c r="B449" t="inlineStr">
@@ -7612,7 +7624,7 @@
       </c>
     </row>
     <row r="450">
-      <c r="A450" s="1" t="n">
+      <c r="A450" s="2" t="n">
         <v>46145.06841435185</v>
       </c>
       <c r="B450" t="inlineStr">
@@ -7628,7 +7640,7 @@
       </c>
     </row>
     <row r="451">
-      <c r="A451" s="1" t="n">
+      <c r="A451" s="2" t="n">
         <v>46145.20671296296</v>
       </c>
       <c r="B451" t="inlineStr">
@@ -7644,7 +7656,7 @@
       </c>
     </row>
     <row r="452">
-      <c r="A452" s="1" t="n">
+      <c r="A452" s="2" t="n">
         <v>46145.35491898148</v>
       </c>
       <c r="B452" t="inlineStr">
@@ -7660,7 +7672,7 @@
       </c>
     </row>
     <row r="453">
-      <c r="A453" s="1" t="n">
+      <c r="A453" s="2" t="n">
         <v>46145.52814814815</v>
       </c>
       <c r="B453" t="inlineStr">
@@ -7676,7 +7688,7 @@
       </c>
     </row>
     <row r="454">
-      <c r="A454" s="1" t="n">
+      <c r="A454" s="2" t="n">
         <v>46145.69175925926</v>
       </c>
       <c r="B454" t="inlineStr">
@@ -7692,7 +7704,7 @@
       </c>
     </row>
     <row r="455">
-      <c r="A455" s="1" t="n">
+      <c r="A455" s="2" t="n">
         <v>46145.85527777778</v>
       </c>
       <c r="B455" t="inlineStr">
@@ -7708,7 +7720,7 @@
       </c>
     </row>
     <row r="456">
-      <c r="A456" s="1" t="n">
+      <c r="A456" s="2" t="n">
         <v>46146.09436342592</v>
       </c>
       <c r="B456" t="inlineStr">
@@ -7724,7 +7736,7 @@
       </c>
     </row>
     <row r="457">
-      <c r="A457" s="1" t="n">
+      <c r="A457" s="2" t="n">
         <v>46146.21984953704</v>
       </c>
       <c r="B457" t="inlineStr">
@@ -7740,7 +7752,7 @@
       </c>
     </row>
     <row r="458">
-      <c r="A458" s="1" t="n">
+      <c r="A458" s="2" t="n">
         <v>46116.3550925926</v>
       </c>
       <c r="B458" t="inlineStr">
@@ -7756,7 +7768,7 @@
       </c>
     </row>
     <row r="459">
-      <c r="A459" s="1" t="n">
+      <c r="A459" s="2" t="n">
         <v>46116.52167824074</v>
       </c>
       <c r="B459" t="inlineStr">
@@ -7772,7 +7784,7 @@
       </c>
     </row>
     <row r="460">
-      <c r="A460" s="1" t="n">
+      <c r="A460" s="2" t="n">
         <v>46116.69474537037</v>
       </c>
       <c r="B460" t="inlineStr">
@@ -7788,7 +7800,7 @@
       </c>
     </row>
     <row r="461">
-      <c r="A461" s="1" t="n">
+      <c r="A461" s="2" t="n">
         <v>46116.85944444445</v>
       </c>
       <c r="B461" t="inlineStr">
@@ -7804,7 +7816,7 @@
       </c>
     </row>
     <row r="462">
-      <c r="A462" s="1" t="n">
+      <c r="A462" s="2" t="n">
         <v>46117.03664351852</v>
       </c>
       <c r="B462" t="inlineStr">
@@ -7820,7 +7832,7 @@
       </c>
     </row>
     <row r="463">
-      <c r="A463" s="1" t="n">
+      <c r="A463" s="2" t="n">
         <v>46117.24065972222</v>
       </c>
       <c r="B463" t="inlineStr">
@@ -7836,7 +7848,7 @@
       </c>
     </row>
     <row r="464">
-      <c r="A464" s="1" t="n">
+      <c r="A464" s="2" t="n">
         <v>46117.36049768519</v>
       </c>
       <c r="B464" t="inlineStr">
@@ -7852,7 +7864,7 @@
       </c>
     </row>
     <row r="465">
-      <c r="A465" s="1" t="n">
+      <c r="A465" s="2" t="n">
         <v>46117.52633101852</v>
       </c>
       <c r="B465" t="inlineStr">
@@ -7868,7 +7880,7 @@
       </c>
     </row>
     <row r="466">
-      <c r="A466" s="1" t="n">
+      <c r="A466" s="2" t="n">
         <v>46117.69008101852</v>
       </c>
       <c r="B466" t="inlineStr">
@@ -7884,7 +7896,7 @@
       </c>
     </row>
     <row r="467">
-      <c r="A467" s="1" t="n">
+      <c r="A467" s="2" t="n">
         <v>46117.87108796297</v>
       </c>
       <c r="B467" t="inlineStr">
@@ -7900,7 +7912,7 @@
       </c>
     </row>
     <row r="468">
-      <c r="A468" s="1" t="n">
+      <c r="A468" s="2" t="n">
         <v>46118.0265625</v>
       </c>
       <c r="B468" t="inlineStr">
@@ -7916,7 +7928,7 @@
       </c>
     </row>
     <row r="469">
-      <c r="A469" s="1" t="n">
+      <c r="A469" s="2" t="n">
         <v>46118.19368055555</v>
       </c>
       <c r="B469" t="inlineStr">
@@ -7932,7 +7944,7 @@
       </c>
     </row>
     <row r="470">
-      <c r="A470" s="1" t="n">
+      <c r="A470" s="2" t="n">
         <v>46118.36050925926</v>
       </c>
       <c r="B470" t="inlineStr">
@@ -7948,7 +7960,7 @@
       </c>
     </row>
     <row r="471">
-      <c r="A471" s="1" t="n">
+      <c r="A471" s="2" t="n">
         <v>46118.52253472222</v>
       </c>
       <c r="B471" t="inlineStr">
@@ -7964,7 +7976,7 @@
       </c>
     </row>
     <row r="472">
-      <c r="A472" s="1" t="n">
+      <c r="A472" s="2" t="n">
         <v>46118.68907407407</v>
       </c>
       <c r="B472" t="inlineStr">
@@ -7980,7 +7992,7 @@
       </c>
     </row>
     <row r="473">
-      <c r="A473" s="1" t="n">
+      <c r="A473" s="2" t="n">
         <v>46118.8552662037</v>
       </c>
       <c r="B473" t="inlineStr">
@@ -7996,7 +8008,7 @@
       </c>
     </row>
     <row r="474">
-      <c r="A474" s="1" t="n">
+      <c r="A474" s="2" t="n">
         <v>46119.02732638889</v>
       </c>
       <c r="B474" t="inlineStr">
@@ -8012,7 +8024,7 @@
       </c>
     </row>
     <row r="475">
-      <c r="A475" s="1" t="n">
+      <c r="A475" s="2" t="n">
         <v>46120.18833333333</v>
       </c>
       <c r="B475" t="inlineStr">
@@ -8028,7 +8040,7 @@
       </c>
     </row>
     <row r="476">
-      <c r="A476" s="1" t="n">
+      <c r="A476" s="2" t="n">
         <v>46120.52369212963</v>
       </c>
       <c r="B476" t="inlineStr">
@@ -8044,7 +8056,7 @@
       </c>
     </row>
     <row r="477">
-      <c r="A477" s="1" t="n">
+      <c r="A477" s="2" t="n">
         <v>46120.69190972222</v>
       </c>
       <c r="B477" t="inlineStr">
@@ -8060,7 +8072,7 @@
       </c>
     </row>
     <row r="478">
-      <c r="A478" s="1" t="n">
+      <c r="A478" s="2" t="n">
         <v>46120.85443287037</v>
       </c>
       <c r="B478" t="inlineStr">
@@ -8076,7 +8088,7 @@
       </c>
     </row>
     <row r="479">
-      <c r="A479" s="1" t="n">
+      <c r="A479" s="2" t="n">
         <v>46124.39263888889</v>
       </c>
       <c r="B479" t="inlineStr">
@@ -8092,7 +8104,7 @@
       </c>
     </row>
     <row r="480">
-      <c r="A480" s="1" t="n">
+      <c r="A480" s="2" t="n">
         <v>46124.52407407408</v>
       </c>
       <c r="B480" t="inlineStr">
@@ -8108,7 +8120,7 @@
       </c>
     </row>
     <row r="481">
-      <c r="A481" s="1" t="n">
+      <c r="A481" s="2" t="n">
         <v>46124.69166666667</v>
       </c>
       <c r="B481" t="inlineStr">
@@ -8124,7 +8136,7 @@
       </c>
     </row>
     <row r="482">
-      <c r="A482" s="1" t="n">
+      <c r="A482" s="2" t="n">
         <v>46124.85614583334</v>
       </c>
       <c r="B482" t="inlineStr">
@@ -8140,7 +8152,7 @@
       </c>
     </row>
     <row r="483">
-      <c r="A483" s="1" t="n">
+      <c r="A483" s="2" t="n">
         <v>46125.07673611111</v>
       </c>
       <c r="B483" t="inlineStr">
@@ -8156,7 +8168,7 @@
       </c>
     </row>
     <row r="484">
-      <c r="A484" s="1" t="n">
+      <c r="A484" s="2" t="n">
         <v>46125.18878472222</v>
       </c>
       <c r="B484" t="inlineStr">
@@ -8172,7 +8184,7 @@
       </c>
     </row>
     <row r="485">
-      <c r="A485" s="1" t="n">
+      <c r="A485" s="2" t="n">
         <v>46125.37304398148</v>
       </c>
       <c r="B485" t="inlineStr">
@@ -8188,7 +8200,7 @@
       </c>
     </row>
     <row r="486">
-      <c r="A486" s="1" t="n">
+      <c r="A486" s="2" t="n">
         <v>46125.52486111111</v>
       </c>
       <c r="B486" t="inlineStr">
@@ -8204,7 +8216,7 @@
       </c>
     </row>
     <row r="487">
-      <c r="A487" s="1" t="n">
+      <c r="A487" s="2" t="n">
         <v>46125.69287037037</v>
       </c>
       <c r="B487" t="inlineStr">
@@ -8220,7 +8232,7 @@
       </c>
     </row>
     <row r="488">
-      <c r="A488" s="1" t="n">
+      <c r="A488" s="2" t="n">
         <v>46125.85716435185</v>
       </c>
       <c r="B488" t="inlineStr">
@@ -8236,7 +8248,7 @@
       </c>
     </row>
     <row r="489">
-      <c r="A489" s="1" t="n">
+      <c r="A489" s="2" t="n">
         <v>46126.03134259259</v>
       </c>
       <c r="B489" t="inlineStr">
@@ -8252,7 +8264,7 @@
       </c>
     </row>
     <row r="490">
-      <c r="A490" s="1" t="n">
+      <c r="A490" s="2" t="n">
         <v>46126.21274305556</v>
       </c>
       <c r="B490" t="inlineStr">
@@ -8268,7 +8280,7 @@
       </c>
     </row>
     <row r="491">
-      <c r="A491" s="1" t="n">
+      <c r="A491" s="2" t="n">
         <v>46126.35861111111</v>
       </c>
       <c r="B491" t="inlineStr">
@@ -8284,7 +8296,7 @@
       </c>
     </row>
     <row r="492">
-      <c r="A492" s="1" t="n">
+      <c r="A492" s="2" t="n">
         <v>46126.53461805556</v>
       </c>
       <c r="B492" t="inlineStr">
@@ -8300,7 +8312,7 @@
       </c>
     </row>
     <row r="493">
-      <c r="A493" s="1" t="n">
+      <c r="A493" s="2" t="n">
         <v>46126.70118055555</v>
       </c>
       <c r="B493" t="inlineStr">
@@ -8316,7 +8328,7 @@
       </c>
     </row>
     <row r="494">
-      <c r="A494" s="1" t="n">
+      <c r="A494" s="2" t="n">
         <v>46126.87692129629</v>
       </c>
       <c r="B494" t="inlineStr">
@@ -8332,7 +8344,7 @@
       </c>
     </row>
     <row r="495">
-      <c r="A495" s="1" t="n">
+      <c r="A495" s="2" t="n">
         <v>46127.02172453704</v>
       </c>
       <c r="B495" t="inlineStr">
@@ -8348,7 +8360,7 @@
       </c>
     </row>
     <row r="496">
-      <c r="A496" s="1" t="n">
+      <c r="A496" s="2" t="n">
         <v>46127.20758101852</v>
       </c>
       <c r="B496" t="inlineStr">
@@ -8364,7 +8376,7 @@
       </c>
     </row>
     <row r="497">
-      <c r="A497" s="1" t="n">
+      <c r="A497" s="2" t="n">
         <v>46127.35572916667</v>
       </c>
       <c r="B497" t="inlineStr">
@@ -8380,7 +8392,7 @@
       </c>
     </row>
     <row r="498">
-      <c r="A498" s="1" t="n">
+      <c r="A498" s="2" t="n">
         <v>46127.53050925926</v>
       </c>
       <c r="B498" t="inlineStr">
@@ -8396,7 +8408,7 @@
       </c>
     </row>
     <row r="499">
-      <c r="A499" s="1" t="n">
+      <c r="A499" s="2" t="n">
         <v>46127.69168981481</v>
       </c>
       <c r="B499" t="inlineStr">
@@ -8412,7 +8424,7 @@
       </c>
     </row>
     <row r="500">
-      <c r="A500" s="1" t="n">
+      <c r="A500" s="2" t="n">
         <v>46127.85546296297</v>
       </c>
       <c r="B500" t="inlineStr">
@@ -8428,7 +8440,7 @@
       </c>
     </row>
     <row r="501">
-      <c r="A501" s="1" t="n">
+      <c r="A501" s="2" t="n">
         <v>46128.04122685185</v>
       </c>
       <c r="B501" t="inlineStr">
@@ -8444,7 +8456,7 @@
       </c>
     </row>
     <row r="502">
-      <c r="A502" s="1" t="n">
+      <c r="A502" s="2" t="n">
         <v>46128.19846064815</v>
       </c>
       <c r="B502" t="inlineStr">
@@ -8460,7 +8472,7 @@
       </c>
     </row>
     <row r="503">
-      <c r="A503" s="1" t="n">
+      <c r="A503" s="2" t="n">
         <v>46128.3578125</v>
       </c>
       <c r="B503" t="inlineStr">
@@ -8476,7 +8488,7 @@
       </c>
     </row>
     <row r="504">
-      <c r="A504" s="1" t="n">
+      <c r="A504" s="2" t="n">
         <v>46128.52149305555</v>
       </c>
       <c r="B504" t="inlineStr">
@@ -8492,7 +8504,7 @@
       </c>
     </row>
     <row r="505">
-      <c r="A505" s="1" t="n">
+      <c r="A505" s="2" t="n">
         <v>46128.69186342593</v>
       </c>
       <c r="B505" t="inlineStr">
@@ -8508,7 +8520,7 @@
       </c>
     </row>
     <row r="506">
-      <c r="A506" s="1" t="n">
+      <c r="A506" s="2" t="n">
         <v>46128.85454861111</v>
       </c>
       <c r="B506" t="inlineStr">
@@ -8524,7 +8536,7 @@
       </c>
     </row>
     <row r="507">
-      <c r="A507" s="1" t="n">
+      <c r="A507" s="2" t="n">
         <v>46129.08709490741</v>
       </c>
       <c r="B507" t="inlineStr">
@@ -8540,7 +8552,7 @@
       </c>
     </row>
     <row r="508">
-      <c r="A508" s="1" t="n">
+      <c r="A508" s="2" t="n">
         <v>46129.20550925926</v>
       </c>
       <c r="B508" t="inlineStr">
@@ -8556,7 +8568,7 @@
       </c>
     </row>
     <row r="509">
-      <c r="A509" s="1" t="n">
+      <c r="A509" s="2" t="n">
         <v>46129.36481481481</v>
       </c>
       <c r="B509" t="inlineStr">
@@ -8572,7 +8584,7 @@
       </c>
     </row>
     <row r="510">
-      <c r="A510" s="1" t="n">
+      <c r="A510" s="2" t="n">
         <v>46129.52703703703</v>
       </c>
       <c r="B510" t="inlineStr">
@@ -8588,7 +8600,7 @@
       </c>
     </row>
     <row r="511">
-      <c r="A511" s="1" t="n">
+      <c r="A511" s="2" t="n">
         <v>46129.69325231481</v>
       </c>
       <c r="B511" t="inlineStr">
@@ -8604,7 +8616,7 @@
       </c>
     </row>
     <row r="512">
-      <c r="A512" s="1" t="n">
+      <c r="A512" s="2" t="n">
         <v>46129.85914351852</v>
       </c>
       <c r="B512" t="inlineStr">
@@ -8620,7 +8632,7 @@
       </c>
     </row>
     <row r="513">
-      <c r="A513" s="1" t="n">
+      <c r="A513" s="2" t="n">
         <v>46130.09744212963</v>
       </c>
       <c r="B513" t="inlineStr">
@@ -8636,7 +8648,7 @@
       </c>
     </row>
     <row r="514">
-      <c r="A514" s="1" t="n">
+      <c r="A514" s="2" t="n">
         <v>46130.19385416667</v>
       </c>
       <c r="B514" t="inlineStr">
@@ -8652,7 +8664,7 @@
       </c>
     </row>
     <row r="515">
-      <c r="A515" s="1" t="n">
+      <c r="A515" s="2" t="n">
         <v>46130.35618055556</v>
       </c>
       <c r="B515" t="inlineStr">
@@ -8668,7 +8680,7 @@
       </c>
     </row>
     <row r="516">
-      <c r="A516" s="1" t="n">
+      <c r="A516" s="2" t="n">
         <v>46130.52403935185</v>
       </c>
       <c r="B516" t="inlineStr">
@@ -8684,7 +8696,7 @@
       </c>
     </row>
     <row r="517">
-      <c r="A517" s="1" t="n">
+      <c r="A517" s="2" t="n">
         <v>46130.68988425926</v>
       </c>
       <c r="B517" t="inlineStr">
@@ -8700,7 +8712,7 @@
       </c>
     </row>
     <row r="518">
-      <c r="A518" s="1" t="n">
+      <c r="A518" s="2" t="n">
         <v>46131.02777777778</v>
       </c>
       <c r="B518" t="inlineStr">
@@ -8716,7 +8728,7 @@
       </c>
     </row>
     <row r="519">
-      <c r="A519" s="1" t="n">
+      <c r="A519" s="2" t="n">
         <v>46131.19017361111</v>
       </c>
       <c r="B519" t="inlineStr">
@@ -8732,7 +8744,7 @@
       </c>
     </row>
     <row r="520">
-      <c r="A520" s="1" t="n">
+      <c r="A520" s="2" t="n">
         <v>46131.35472222222</v>
       </c>
       <c r="B520" t="inlineStr">
@@ -8748,7 +8760,7 @@
       </c>
     </row>
     <row r="521">
-      <c r="A521" s="1" t="n">
+      <c r="A521" s="2" t="n">
         <v>46131.52929398148</v>
       </c>
       <c r="B521" t="inlineStr">
@@ -8764,7 +8776,7 @@
       </c>
     </row>
     <row r="522">
-      <c r="A522" s="1" t="n">
+      <c r="A522" s="2" t="n">
         <v>46131.68760416667</v>
       </c>
       <c r="B522" t="inlineStr">
@@ -8780,7 +8792,7 @@
       </c>
     </row>
     <row r="523">
-      <c r="A523" s="1" t="n">
+      <c r="A523" s="2" t="n">
         <v>46131.8633912037</v>
       </c>
       <c r="B523" t="inlineStr">
@@ -8796,7 +8808,7 @@
       </c>
     </row>
     <row r="524">
-      <c r="A524" s="1" t="n">
+      <c r="A524" s="2" t="n">
         <v>46132.02103009259</v>
       </c>
       <c r="B524" t="inlineStr">
@@ -8812,7 +8824,7 @@
       </c>
     </row>
     <row r="525">
-      <c r="A525" s="1" t="n">
+      <c r="A525" s="2" t="n">
         <v>46132.19717592592</v>
       </c>
       <c r="B525" t="inlineStr">
@@ -8828,7 +8840,7 @@
       </c>
     </row>
     <row r="526">
-      <c r="A526" s="1" t="n">
+      <c r="A526" s="2" t="n">
         <v>46132.3584375</v>
       </c>
       <c r="B526" t="inlineStr">
@@ -8844,7 +8856,7 @@
       </c>
     </row>
     <row r="527">
-      <c r="A527" s="1" t="n">
+      <c r="A527" s="2" t="n">
         <v>46132.52159722222</v>
       </c>
       <c r="B527" t="inlineStr">
@@ -8860,7 +8872,7 @@
       </c>
     </row>
     <row r="528">
-      <c r="A528" s="1" t="n">
+      <c r="A528" s="2" t="n">
         <v>46132.69394675926</v>
       </c>
       <c r="B528" t="inlineStr">
@@ -8876,7 +8888,7 @@
       </c>
     </row>
     <row r="529">
-      <c r="A529" s="1" t="n">
+      <c r="A529" s="2" t="n">
         <v>46132.86247685185</v>
       </c>
       <c r="B529" t="inlineStr">
@@ -8892,7 +8904,7 @@
       </c>
     </row>
     <row r="530">
-      <c r="A530" s="1" t="n">
+      <c r="A530" s="2" t="n">
         <v>46133.07111111111</v>
       </c>
       <c r="B530" t="inlineStr">
@@ -8908,7 +8920,7 @@
       </c>
     </row>
     <row r="531">
-      <c r="A531" s="1" t="n">
+      <c r="A531" s="2" t="n">
         <v>46133.19524305555</v>
       </c>
       <c r="B531" t="inlineStr">
@@ -8924,7 +8936,7 @@
       </c>
     </row>
     <row r="532">
-      <c r="A532" s="1" t="n">
+      <c r="A532" s="2" t="n">
         <v>46133.36118055556</v>
       </c>
       <c r="B532" t="inlineStr">
@@ -8940,7 +8952,7 @@
       </c>
     </row>
     <row r="533">
-      <c r="A533" s="1" t="n">
+      <c r="A533" s="2" t="n">
         <v>46133.52528935186</v>
       </c>
       <c r="B533" t="inlineStr">
@@ -8956,7 +8968,7 @@
       </c>
     </row>
     <row r="534">
-      <c r="A534" s="1" t="n">
+      <c r="A534" s="2" t="n">
         <v>46133.69530092592</v>
       </c>
       <c r="B534" t="inlineStr">
@@ -8972,7 +8984,7 @@
       </c>
     </row>
     <row r="535">
-      <c r="A535" s="1" t="n">
+      <c r="A535" s="2" t="n">
         <v>46133.85505787037</v>
       </c>
       <c r="B535" t="inlineStr">
@@ -8988,7 +9000,7 @@
       </c>
     </row>
     <row r="536">
-      <c r="A536" s="1" t="n">
+      <c r="A536" s="2" t="n">
         <v>46134.09811342593</v>
       </c>
       <c r="B536" t="inlineStr">
@@ -9004,7 +9016,7 @@
       </c>
     </row>
     <row r="537">
-      <c r="A537" s="1" t="n">
+      <c r="A537" s="2" t="n">
         <v>46134.21712962963</v>
       </c>
       <c r="B537" t="inlineStr">
@@ -9020,7 +9032,7 @@
       </c>
     </row>
     <row r="538">
-      <c r="A538" s="1" t="n">
+      <c r="A538" s="2" t="n">
         <v>46134.35688657407</v>
       </c>
       <c r="B538" t="inlineStr">
@@ -9036,7 +9048,7 @@
       </c>
     </row>
     <row r="539">
-      <c r="A539" s="1" t="n">
+      <c r="A539" s="2" t="n">
         <v>46134.52453703704</v>
       </c>
       <c r="B539" t="inlineStr">
@@ -9052,7 +9064,7 @@
       </c>
     </row>
     <row r="540">
-      <c r="A540" s="1" t="n">
+      <c r="A540" s="2" t="n">
         <v>46134.72311342593</v>
       </c>
       <c r="B540" t="inlineStr">
@@ -9068,7 +9080,7 @@
       </c>
     </row>
     <row r="541">
-      <c r="A541" s="1" t="n">
+      <c r="A541" s="2" t="n">
         <v>46134.85905092592</v>
       </c>
       <c r="B541" t="inlineStr">
@@ -9084,7 +9096,7 @@
       </c>
     </row>
     <row r="542">
-      <c r="A542" s="1" t="n">
+      <c r="A542" s="2" t="n">
         <v>46135.02693287037</v>
       </c>
       <c r="B542" t="inlineStr">
@@ -9100,7 +9112,7 @@
       </c>
     </row>
     <row r="543">
-      <c r="A543" s="1" t="n">
+      <c r="A543" s="2" t="n">
         <v>46135.19215277778</v>
       </c>
       <c r="B543" t="inlineStr">
@@ -9116,7 +9128,7 @@
       </c>
     </row>
     <row r="544">
-      <c r="A544" s="1" t="n">
+      <c r="A544" s="2" t="n">
         <v>46135.3603125</v>
       </c>
       <c r="B544" t="inlineStr">
@@ -9132,7 +9144,7 @@
       </c>
     </row>
     <row r="545">
-      <c r="A545" s="1" t="n">
+      <c r="A545" s="2" t="n">
         <v>46135.53359953704</v>
       </c>
       <c r="B545" t="inlineStr">
@@ -9148,7 +9160,7 @@
       </c>
     </row>
     <row r="546">
-      <c r="A546" s="1" t="n">
+      <c r="A546" s="2" t="n">
         <v>46135.68820601852</v>
       </c>
       <c r="B546" t="inlineStr">
@@ -9164,7 +9176,7 @@
       </c>
     </row>
     <row r="547">
-      <c r="A547" s="1" t="n">
+      <c r="A547" s="2" t="n">
         <v>46135.86390046297</v>
       </c>
       <c r="B547" t="inlineStr">
@@ -9180,7 +9192,7 @@
       </c>
     </row>
     <row r="548">
-      <c r="A548" s="1" t="n">
+      <c r="A548" s="2" t="n">
         <v>46136.02126157407</v>
       </c>
       <c r="B548" t="inlineStr">
@@ -9196,7 +9208,7 @@
       </c>
     </row>
     <row r="549">
-      <c r="A549" s="1" t="n">
+      <c r="A549" s="2" t="n">
         <v>46136.18943287037</v>
       </c>
       <c r="B549" t="inlineStr">
@@ -9212,7 +9224,7 @@
       </c>
     </row>
     <row r="550">
-      <c r="A550" s="1" t="n">
+      <c r="A550" s="2" t="n">
         <v>46136.35768518518</v>
       </c>
       <c r="B550" t="inlineStr">
@@ -9228,7 +9240,7 @@
       </c>
     </row>
     <row r="551">
-      <c r="A551" s="1" t="n">
+      <c r="A551" s="2" t="n">
         <v>46136.52224537037</v>
       </c>
       <c r="B551" t="inlineStr">
@@ -9244,7 +9256,7 @@
       </c>
     </row>
     <row r="552">
-      <c r="A552" s="1" t="n">
+      <c r="A552" s="2" t="n">
         <v>46136.6883912037</v>
       </c>
       <c r="B552" t="inlineStr">
@@ -9260,7 +9272,7 @@
       </c>
     </row>
     <row r="553">
-      <c r="A553" s="1" t="n">
+      <c r="A553" s="2" t="n">
         <v>46136.85456018519</v>
       </c>
       <c r="B553" t="inlineStr">
@@ -9276,7 +9288,7 @@
       </c>
     </row>
     <row r="554">
-      <c r="A554" s="1" t="n">
+      <c r="A554" s="2" t="n">
         <v>46137.0588425926</v>
       </c>
       <c r="B554" t="inlineStr">
@@ -9292,7 +9304,7 @@
       </c>
     </row>
     <row r="555">
-      <c r="A555" s="1" t="n">
+      <c r="A555" s="2" t="n">
         <v>46137.18950231482</v>
       </c>
       <c r="B555" t="inlineStr">
@@ -9308,7 +9320,7 @@
       </c>
     </row>
     <row r="556">
-      <c r="A556" s="1" t="n">
+      <c r="A556" s="2" t="n">
         <v>46137.36697916667</v>
       </c>
       <c r="B556" t="inlineStr">
@@ -9324,7 +9336,7 @@
       </c>
     </row>
     <row r="557">
-      <c r="A557" s="1" t="n">
+      <c r="A557" s="2" t="n">
         <v>46137.52636574074</v>
       </c>
       <c r="B557" t="inlineStr">
@@ -9340,7 +9352,7 @@
       </c>
     </row>
     <row r="558">
-      <c r="A558" s="1" t="n">
+      <c r="A558" s="2" t="n">
         <v>46137.68905092592</v>
       </c>
       <c r="B558" t="inlineStr">
@@ -9356,7 +9368,7 @@
       </c>
     </row>
     <row r="559">
-      <c r="A559" s="1" t="n">
+      <c r="A559" s="2" t="n">
         <v>46137.8555787037</v>
       </c>
       <c r="B559" t="inlineStr">
@@ -9372,7 +9384,7 @@
       </c>
     </row>
     <row r="560">
-      <c r="A560" s="1" t="n">
+      <c r="A560" s="2" t="n">
         <v>46138.08900462963</v>
       </c>
       <c r="B560" t="inlineStr">
@@ -9388,7 +9400,7 @@
       </c>
     </row>
     <row r="561">
-      <c r="A561" s="1" t="n">
+      <c r="A561" s="2" t="n">
         <v>46138.22342592593</v>
       </c>
       <c r="B561" t="inlineStr">
@@ -9404,7 +9416,7 @@
       </c>
     </row>
     <row r="562">
-      <c r="A562" s="1" t="n">
+      <c r="A562" s="2" t="n">
         <v>46138.35784722222</v>
       </c>
       <c r="B562" t="inlineStr">
@@ -9420,7 +9432,7 @@
       </c>
     </row>
     <row r="563">
-      <c r="A563" s="1" t="n">
+      <c r="A563" s="2" t="n">
         <v>46138.54626157408</v>
       </c>
       <c r="B563" t="inlineStr">
@@ -9436,7 +9448,7 @@
       </c>
     </row>
     <row r="564">
-      <c r="A564" s="1" t="n">
+      <c r="A564" s="2" t="n">
         <v>46138.69407407408</v>
       </c>
       <c r="B564" t="inlineStr">
@@ -9452,7 +9464,7 @@
       </c>
     </row>
     <row r="565">
-      <c r="A565" s="1" t="n">
+      <c r="A565" s="2" t="n">
         <v>46138.85946759259</v>
       </c>
       <c r="B565" t="inlineStr">
@@ -9468,7 +9480,7 @@
       </c>
     </row>
     <row r="566">
-      <c r="A566" s="1" t="n">
+      <c r="A566" s="2" t="n">
         <v>46139.04685185185</v>
       </c>
       <c r="B566" t="inlineStr">
@@ -9484,7 +9496,7 @@
       </c>
     </row>
     <row r="567">
-      <c r="A567" s="1" t="n">
+      <c r="A567" s="2" t="n">
         <v>46139.20314814815</v>
       </c>
       <c r="B567" t="inlineStr">
@@ -9500,7 +9512,7 @@
       </c>
     </row>
     <row r="568">
-      <c r="A568" s="1" t="n">
+      <c r="A568" s="2" t="n">
         <v>46139.35634259259</v>
       </c>
       <c r="B568" t="inlineStr">
@@ -9516,7 +9528,7 @@
       </c>
     </row>
     <row r="569">
-      <c r="A569" s="1" t="n">
+      <c r="A569" s="2" t="n">
         <v>46139.52431712963</v>
       </c>
       <c r="B569" t="inlineStr">
@@ -9532,7 +9544,7 @@
       </c>
     </row>
     <row r="570">
-      <c r="A570" s="1" t="n">
+      <c r="A570" s="2" t="n">
         <v>46139.69873842593</v>
       </c>
       <c r="B570" t="inlineStr">
@@ -9548,7 +9560,7 @@
       </c>
     </row>
     <row r="571">
-      <c r="A571" s="1" t="n">
+      <c r="A571" s="2" t="n">
         <v>46139.86931712963</v>
       </c>
       <c r="B571" t="inlineStr">
@@ -9564,7 +9576,7 @@
       </c>
     </row>
     <row r="572">
-      <c r="A572" s="1" t="n">
+      <c r="A572" s="2" t="n">
         <v>46140.02158564814</v>
       </c>
       <c r="B572" t="inlineStr">
@@ -9580,7 +9592,7 @@
       </c>
     </row>
     <row r="573">
-      <c r="A573" s="1" t="n">
+      <c r="A573" s="2" t="n">
         <v>46140.19370370371</v>
       </c>
       <c r="B573" t="inlineStr">
@@ -9596,7 +9608,7 @@
       </c>
     </row>
     <row r="574">
-      <c r="A574" s="1" t="n">
+      <c r="A574" s="2" t="n">
         <v>46140.35989583333</v>
       </c>
       <c r="B574" t="inlineStr">
@@ -9612,7 +9624,7 @@
       </c>
     </row>
     <row r="575">
-      <c r="A575" s="1" t="n">
+      <c r="A575" s="2" t="n">
         <v>46140.52547453704</v>
       </c>
       <c r="B575" t="inlineStr">
@@ -9628,7 +9640,7 @@
       </c>
     </row>
     <row r="576">
-      <c r="A576" s="1" t="n">
+      <c r="A576" s="2" t="n">
         <v>46140.69204861111</v>
       </c>
       <c r="B576" t="inlineStr">
@@ -9644,7 +9656,7 @@
       </c>
     </row>
     <row r="577">
-      <c r="A577" s="1" t="n">
+      <c r="A577" s="2" t="n">
         <v>46140.85797453704</v>
       </c>
       <c r="B577" t="inlineStr">
@@ -9660,7 +9672,7 @@
       </c>
     </row>
     <row r="578">
-      <c r="A578" s="1" t="n">
+      <c r="A578" s="2" t="n">
         <v>46141.08907407407</v>
       </c>
       <c r="B578" t="inlineStr">
@@ -9676,7 +9688,7 @@
       </c>
     </row>
     <row r="579">
-      <c r="A579" s="1" t="n">
+      <c r="A579" s="2" t="n">
         <v>46141.19405092593</v>
       </c>
       <c r="B579" t="inlineStr">
@@ -9692,7 +9704,7 @@
       </c>
     </row>
     <row r="580">
-      <c r="A580" s="1" t="n">
+      <c r="A580" s="2" t="n">
         <v>46141.37282407407</v>
       </c>
       <c r="B580" t="inlineStr">
@@ -9708,7 +9720,7 @@
       </c>
     </row>
     <row r="581">
-      <c r="A581" s="1" t="n">
+      <c r="A581" s="2" t="n">
         <v>46141.52434027778</v>
       </c>
       <c r="B581" t="inlineStr">
@@ -9724,7 +9736,7 @@
       </c>
     </row>
     <row r="582">
-      <c r="A582" s="1" t="n">
+      <c r="A582" s="2" t="n">
         <v>46141.69369212963</v>
       </c>
       <c r="B582" t="inlineStr">
@@ -9740,7 +9752,7 @@
       </c>
     </row>
     <row r="583">
-      <c r="A583" s="1" t="n">
+      <c r="A583" s="2" t="n">
         <v>46141.85452546296</v>
       </c>
       <c r="B583" t="inlineStr">
@@ -9756,7 +9768,7 @@
       </c>
     </row>
     <row r="584">
-      <c r="A584" s="1" t="n">
+      <c r="A584" s="2" t="n">
         <v>46142.09556712963</v>
       </c>
       <c r="B584" t="inlineStr">
@@ -9772,7 +9784,7 @@
       </c>
     </row>
     <row r="585">
-      <c r="A585" s="1" t="n">
+      <c r="A585" s="2" t="n">
         <v>46142.22015046296</v>
       </c>
       <c r="B585" t="inlineStr">
@@ -9788,7 +9800,7 @@
       </c>
     </row>
     <row r="586">
-      <c r="A586" s="1" t="n">
+      <c r="A586" s="2" t="n">
         <v>46142.35427083333</v>
       </c>
       <c r="B586" t="inlineStr">
@@ -9804,7 +9816,7 @@
       </c>
     </row>
     <row r="587">
-      <c r="A587" s="1" t="n">
+      <c r="A587" s="2" t="n">
         <v>46142.52810185185</v>
       </c>
       <c r="B587" t="inlineStr">
@@ -9820,7 +9832,7 @@
       </c>
     </row>
     <row r="588">
-      <c r="A588" s="1" t="n">
+      <c r="A588" s="2" t="n">
         <v>46142.70089120371</v>
       </c>
       <c r="B588" t="inlineStr">
@@ -9836,7 +9848,7 @@
       </c>
     </row>
     <row r="589">
-      <c r="A589" s="1" t="n">
+      <c r="A589" s="2" t="n">
         <v>46142.85965277778</v>
       </c>
       <c r="B589" t="inlineStr">
@@ -9852,7 +9864,7 @@
       </c>
     </row>
     <row r="590">
-      <c r="A590" s="1" t="n">
+      <c r="A590" s="2" t="n">
         <v>46143.02594907407</v>
       </c>
       <c r="B590" t="inlineStr">
@@ -9868,7 +9880,7 @@
       </c>
     </row>
     <row r="591">
-      <c r="A591" s="1" t="n">
+      <c r="A591" s="2" t="n">
         <v>46143.20488425926</v>
       </c>
       <c r="B591" t="inlineStr">
@@ -9884,7 +9896,7 @@
       </c>
     </row>
     <row r="592">
-      <c r="A592" s="1" t="n">
+      <c r="A592" s="2" t="n">
         <v>46143.35506944444</v>
       </c>
       <c r="B592" t="inlineStr">
@@ -9900,7 +9912,7 @@
       </c>
     </row>
     <row r="593">
-      <c r="A593" s="1" t="n">
+      <c r="A593" s="2" t="n">
         <v>46143.52101851852</v>
       </c>
       <c r="B593" t="inlineStr">
@@ -9916,7 +9928,7 @@
       </c>
     </row>
     <row r="594">
-      <c r="A594" s="1" t="n">
+      <c r="A594" s="2" t="n">
         <v>46143.69318287037</v>
       </c>
       <c r="B594" t="inlineStr">
@@ -9932,7 +9944,7 @@
       </c>
     </row>
     <row r="595">
-      <c r="A595" s="1" t="n">
+      <c r="A595" s="2" t="n">
         <v>46143.86835648148</v>
       </c>
       <c r="B595" t="inlineStr">
@@ -9948,7 +9960,7 @@
       </c>
     </row>
     <row r="596">
-      <c r="A596" s="1" t="n">
+      <c r="A596" s="2" t="n">
         <v>46144.02177083334</v>
       </c>
       <c r="B596" t="inlineStr">
@@ -9964,7 +9976,7 @@
       </c>
     </row>
     <row r="597">
-      <c r="A597" s="1" t="n">
+      <c r="A597" s="2" t="n">
         <v>46144.18803240741</v>
       </c>
       <c r="B597" t="inlineStr">
@@ -9980,7 +9992,7 @@
       </c>
     </row>
     <row r="598">
-      <c r="A598" s="1" t="n">
+      <c r="A598" s="2" t="n">
         <v>46144.35827546296</v>
       </c>
       <c r="B598" t="inlineStr">
@@ -9996,7 +10008,7 @@
       </c>
     </row>
     <row r="599">
-      <c r="A599" s="1" t="n">
+      <c r="A599" s="2" t="n">
         <v>46144.52101851852</v>
       </c>
       <c r="B599" t="inlineStr">
@@ -10012,7 +10024,7 @@
       </c>
     </row>
     <row r="600">
-      <c r="A600" s="1" t="n">
+      <c r="A600" s="2" t="n">
         <v>46144.69450231481</v>
       </c>
       <c r="B600" t="inlineStr">
@@ -10028,7 +10040,7 @@
       </c>
     </row>
     <row r="601">
-      <c r="A601" s="1" t="n">
+      <c r="A601" s="2" t="n">
         <v>46144.85748842593</v>
       </c>
       <c r="B601" t="inlineStr">
@@ -10044,7 +10056,7 @@
       </c>
     </row>
     <row r="602">
-      <c r="A602" s="1" t="n">
+      <c r="A602" s="2" t="n">
         <v>46145.06841435185</v>
       </c>
       <c r="B602" t="inlineStr">
@@ -10060,7 +10072,7 @@
       </c>
     </row>
     <row r="603">
-      <c r="A603" s="1" t="n">
+      <c r="A603" s="2" t="n">
         <v>46145.20671296296</v>
       </c>
       <c r="B603" t="inlineStr">
@@ -10076,7 +10088,7 @@
       </c>
     </row>
     <row r="604">
-      <c r="A604" s="1" t="n">
+      <c r="A604" s="2" t="n">
         <v>46145.35491898148</v>
       </c>
       <c r="B604" t="inlineStr">
@@ -10092,7 +10104,7 @@
       </c>
     </row>
     <row r="605">
-      <c r="A605" s="1" t="n">
+      <c r="A605" s="2" t="n">
         <v>46145.52814814815</v>
       </c>
       <c r="B605" t="inlineStr">
@@ -10108,7 +10120,7 @@
       </c>
     </row>
     <row r="606">
-      <c r="A606" s="1" t="n">
+      <c r="A606" s="2" t="n">
         <v>46145.69175925926</v>
       </c>
       <c r="B606" t="inlineStr">
@@ -10124,7 +10136,7 @@
       </c>
     </row>
     <row r="607">
-      <c r="A607" s="1" t="n">
+      <c r="A607" s="2" t="n">
         <v>46145.85527777778</v>
       </c>
       <c r="B607" t="inlineStr">
@@ -10140,7 +10152,7 @@
       </c>
     </row>
     <row r="608">
-      <c r="A608" s="1" t="n">
+      <c r="A608" s="2" t="n">
         <v>46146.09436342592</v>
       </c>
       <c r="B608" t="inlineStr">
@@ -10156,7 +10168,7 @@
       </c>
     </row>
     <row r="609">
-      <c r="A609" s="1" t="n">
+      <c r="A609" s="2" t="n">
         <v>46146.21984953704</v>
       </c>
       <c r="B609" t="inlineStr">
@@ -10186,27 +10198,27 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>AssetID</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Clean_Mean</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Clean_Std</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Normal_Upper_Limit(3Sigma)</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Outliers_Removed</t>
         </is>
